--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>116.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-613.0%</t>
+          <t>-613.4%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-284.0%</t>
         </is>
       </c>
     </row>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.514534329016779</v>
+        <v>-4.517773496571356</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9231678387594062</v>
+        <v>0.9218721717375753</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.6575987542139436</v>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.1%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.8%</t>
+          <t>439.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-613.4%</t>
+          <t>-630.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-42.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-132.4%</t>
+          <t>-131.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.0%</t>
+          <t>-290.9%</t>
         </is>
       </c>
     </row>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.517773496571356</v>
+        <v>-4.689397606983304</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9218721717375753</v>
+        <v>0.8532225275727958</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.6575987542139436</v>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>135.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-708.7%</t>
+          <t>-689.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-56.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.4%</t>
+          <t>444.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.5%</t>
+          <t>-594.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-276.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-67.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.9%</t>
+          <t>-276.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.7%</t>
+          <t>-159.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.79404482308609</v>
+        <v>-3.601952958808613</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.620116184204063</v>
+        <v>1.696952929915053</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4935892642914559</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.137727596312753</v>
+        <v>-3.945635732035276</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.484412198368014</v>
+        <v>1.561248944079004</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.601495316318674</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.495377946551101</v>
+        <v>-4.303286082273624</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.337458116928932</v>
+        <v>1.414294862639923</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.9591456665570222</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.804612049547152</v>
+        <v>-4.612520185269675</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.215537402430771</v>
+        <v>1.292374148141762</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.9591456665570222</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.236417842696939</v>
+        <v>-5.044325978419463</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.029147972638261</v>
+        <v>1.105984718349251</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.095563162998289</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.471111836829492</v>
+        <v>-5.279019972552015</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9235551499873305</v>
+        <v>1.000391895698321</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.089226895769034</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.806774484059944</v>
+        <v>-5.614682619782467</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7878706827511146</v>
+        <v>0.8647074284621055</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.089226895769034</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.170400728960257</v>
+        <v>-5.978308864682781</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6489077450252307</v>
+        <v>0.7257444907362216</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.18744853263616</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.535528111599004</v>
+        <v>-6.343436247321527</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5021113069755638</v>
+        <v>0.5789480526865542</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.483759316935172</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.944116888779682</v>
+        <v>-6.752025024502206</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3374373401180515</v>
+        <v>0.4142740858290419</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.892348094115851</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.357099372920776</v>
+        <v>-7.1650075086433</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1674297789330748</v>
+        <v>0.2442665246440647</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.892348094115851</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.773491247207773</v>
+        <v>-7.581399382930297</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.001132920172846941</v>
+        <v>0.07570382553814348</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.892348094115851</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.150168257737617</v>
+        <v>-7.958076393460142</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1415450337161053</v>
+        <v>-0.0647082880051153</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.892348094115851</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.496043079722426</v>
+        <v>-8.30395121544495</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2837953973643339</v>
+        <v>-0.2069586516533435</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.892348094115851</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.658185350185519</v>
+        <v>-8.466093485908043</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3502473854945705</v>
+        <v>-0.27341063978358</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.892348094115851</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.954846691995717</v>
+        <v>-8.762754827718242</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4651329462894416</v>
+        <v>-0.3882962005784512</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.961091229849729</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.388195800105953</v>
+        <v>-9.196103935828477</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6424988940679386</v>
+        <v>-0.5656621483569482</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.961091229849729</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.771197188848584</v>
+        <v>-9.579105324571108</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.795801550886575</v>
+        <v>-0.7189648051755846</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.961091229849729</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.928596069061705</v>
+        <v>-9.736504204784229</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8561895870003933</v>
+        <v>-0.7793528412894029</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.11849011006285</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.28812639156571</v>
+        <v>-10.09603452728823</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9946514127039441</v>
+        <v>-0.9178146669929532</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.11849011006285</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.61452642023072</v>
+        <v>-10.42243455595324</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.117295404212772</v>
+        <v>-1.040458658501781</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.444890138727863</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.83367538830492</v>
+        <v>-10.64158352402744</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.201913240820681</v>
+        <v>-1.125076495109691</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.664039106802061</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.82998446334851</v>
+        <v>-10.63789259907103</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.200436870838117</v>
+        <v>-1.123600125127127</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.664039106802061</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.03424263867837</v>
+        <v>-10.84215077440089</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.27662694385142</v>
+        <v>-1.19979019814043</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.79167805141605</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.25228041030955</v>
+        <v>-11.06018854603207</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.359359498019455</v>
+        <v>-1.282522752308465</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.966448819511949</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.1788105786421</v>
+        <v>-10.98671871436462</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.314599863859055</v>
+        <v>-1.237763118148064</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.8929789878445</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.35393499602864</v>
+        <v>-11.16184313175117</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.370094410066155</v>
+        <v>-1.293257664355165</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.068103405231044</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.58838709004313</v>
+        <v>-11.39629522576566</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.471094412573547</v>
+        <v>-1.394257666862556</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.068103405231044</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.87619093458037</v>
+        <v>-11.68409907030289</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.592888141162419</v>
+        <v>-1.516051395451429</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.355907249768282</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.10601538174419</v>
+        <v>-11.91392351746672</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.683702130189393</v>
+        <v>-1.606865384478402</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.518554786838443</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.33804430148046</v>
+        <v>-12.14595243720298</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.773819969454782</v>
+        <v>-1.696983223743792</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.580567484026866</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.28602878751164</v>
+        <v>-12.09393692323417</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.749023428180856</v>
+        <v>-1.672186682469866</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.580567484026866</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.42770062923576</v>
+        <v>-12.23560876495829</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.807167391769246</v>
+        <v>-1.730330646058256</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.580567484026866</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.37810978481093</v>
+        <v>-12.18601792053345</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.77227764383444</v>
+        <v>-1.69544089812345</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.530976639602032</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.17895767757383</v>
+        <v>-11.98686581329635</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.705667934586284</v>
+        <v>-1.628831188875294</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.365654113652219</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.95311252485442</v>
+        <v>-11.76102066057694</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.60575080046231</v>
+        <v>-1.52891405475132</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.323727438065055</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.82853386851683</v>
+        <v>-11.63644200423935</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.554780193371215</v>
+        <v>-1.477943447660224</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.323727438065055</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.88142915656111</v>
+        <v>-11.68933729228364</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.573304534426821</v>
+        <v>-1.496467788715831</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.318772091976609</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.59752042563236</v>
+        <v>-11.40542856135489</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.454007337816686</v>
+        <v>-1.377170592105695</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.318772091976609</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.48209950149427</v>
+        <v>-11.29000763721679</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.417576230555312</v>
+        <v>-1.340739484844322</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.203351167838513</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.2182626342902</v>
+        <v>-11.02617077001272</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.321924964986592</v>
+        <v>-1.245088219275602</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.203351167838513</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9510208334218</v>
+        <v>-10.75892896914432</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.216862805138607</v>
+        <v>-1.140026059427616</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.203351167838513</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.82771490494358</v>
+        <v>-10.63562304066611</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.16784074872078</v>
+        <v>-1.091004003009789</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.11393349671095</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.80376136396762</v>
+        <v>-10.61166949969015</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.157590826184903</v>
+        <v>-1.080754080473912</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.089979955734993</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.53970142564483</v>
+        <v>-10.34760956136735</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.065227167017536</v>
+        <v>-0.988390421306546</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.825920017412197</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.83262180213999</v>
+        <v>-9.640529937862514</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7851823512759024</v>
+        <v>-0.708345605564912</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.825920017412197</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.792437503773799</v>
+        <v>-9.600345639496323</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7687650080415849</v>
+        <v>-0.6919282623305945</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.785735719046006</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.712367708235995</v>
+        <v>-9.520275843958519</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.737370268605706</v>
+        <v>-0.6605335228947156</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.705665923508202</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.478886486006395</v>
+        <v>-9.286794621728919</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.636053350876014</v>
+        <v>-0.5592166051650236</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.472184701278603</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.299177955862522</v>
+        <v>-9.107086091585046</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5670621491314236</v>
+        <v>-0.4902254034204332</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.415013197115907</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.166902482231635</v>
+        <v>-8.974810617954159</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5187844729320417</v>
+        <v>-0.4419477272210512</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.282737723485021</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.976302807558481</v>
+        <v>-8.784210943281005</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4397295423751437</v>
+        <v>-0.3628927966641533</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.092138048811868</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.7273030088749</v>
+        <v>-8.535211144597424</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3272232816780525</v>
+        <v>-0.2503865359670621</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.092138048811868</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.832892998648004</v>
+        <v>-8.640801134370529</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4974352071865127</v>
+        <v>-0.4205984614755227</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.197728038584973</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.851627900766601</v>
+        <v>-8.659536036489126</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4563848261568655</v>
+        <v>-0.3795480804458751</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.197728038584973</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.703687859359002</v>
+        <v>-8.511595995081526</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5170877322819933</v>
+        <v>-0.4402509865710029</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.177407122676415</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.67945922297003</v>
+        <v>-8.487367358692554</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5161102639798822</v>
+        <v>-0.4392735182688918</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.153178486287443</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.635910816199338</v>
+        <v>-8.443818951921862</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5056515133666988</v>
+        <v>-0.4288147676557088</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.153178486287443</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.39376242274548</v>
+        <v>-8.201670558468004</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3943298016040124</v>
+        <v>-0.3174930558930225</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.153178486287443</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.330533050977133</v>
+        <v>-8.138441186699657</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3745059324374784</v>
+        <v>-0.2976691867264885</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.153178486287443</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.207241916160003</v>
+        <v>-8.015150051882527</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3276913845000498</v>
+        <v>-0.2508546387890593</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.029887351470312</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.18609271725656</v>
+        <v>-7.994000852979084</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3115307267013474</v>
+        <v>-0.234693980990357</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.008738152566869</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.942327275273116</v>
+        <v>-7.750235410995639</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2182438415609194</v>
+        <v>-0.1414070958499285</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.008738152566869</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.678299208079856</v>
+        <v>-7.486207343802379</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1105083007635992</v>
+        <v>-0.03367155505260833</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.806872753750915</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.428448814130782</v>
+        <v>-7.236356949853304</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.01782606820026755</v>
+        <v>0.05901067751072375</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.806872753750915</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.25255672166335</v>
+        <v>-7.060464857385872</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.0561298923073541</v>
+        <v>0.1329666380183454</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.806872753750915</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.081110258640886</v>
+        <v>-6.889018394363409</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1380359835708931</v>
+        <v>0.2148727292818844</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.635426290728452</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.856077258972063</v>
+        <v>-6.663985394694586</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2270696610547196</v>
+        <v>0.3039064067657105</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.410393291059629</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.641442881335657</v>
+        <v>-6.449351017058179</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3176182131635996</v>
+        <v>0.3944549588745905</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.195758913423222</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.374842524361305</v>
+        <v>-6.182750660083827</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4054526147371358</v>
+        <v>0.4822893604481266</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.195758913423222</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.134412027556444</v>
+        <v>-5.942320163278967</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5033678900839571</v>
+        <v>0.5802046357949484</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9553284166183622</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.891621219906999</v>
+        <v>-5.699529355629521</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6044135269785555</v>
+        <v>0.6812502726895469</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9553284166183622</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.775681370281814</v>
+        <v>-5.583589506004336</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.65146805074597</v>
+        <v>0.7283047964569609</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8785066856022383</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.533025781858651</v>
+        <v>-5.340933917581173</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7455283573352283</v>
+        <v>0.8223651030462196</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8785066856022383</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.31300498382164</v>
+        <v>-5.120913119544163</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8351157135606466</v>
+        <v>0.9119524592716379</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7372868405342581</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.113756353916831</v>
+        <v>-4.921664489639354</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9307093483243936</v>
+        <v>1.007546094035385</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7372868405342581</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.954241250397462</v>
+        <v>-4.762149386119984</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9956612341724436</v>
+        <v>1.072497979883435</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5777717370148882</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.809569105297724</v>
+        <v>-4.617477241020246</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.063618194773778</v>
+        <v>1.140454940484769</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.4330995919151507</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.869443932655416</v>
+        <v>-4.677352068377939</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.025705755232127</v>
+        <v>1.102542500943118</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4929744192728429</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.782644434876408</v>
+        <v>-4.590552570598931</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.082826047666297</v>
+        <v>1.159662793377288</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4929744192728429</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.785114141338214</v>
+        <v>-4.593022277060737</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.081910566454986</v>
+        <v>1.158747312165977</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.495444125734649</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.853484327662224</v>
+        <v>-4.661392463384747</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.065569414400084</v>
+        <v>1.142406160111075</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4861684266984341</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.732067898035748</v>
+        <v>-4.53997603375827</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.104572694882566</v>
+        <v>1.181409440593557</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4861684266984341</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.763061057364453</v>
+        <v>-4.570969193086976</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9168849961914709</v>
+        <v>0.993721741902462</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4861684266984341</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.587586797571984</v>
+        <v>-4.395494933294506</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9916419321002465</v>
+        <v>1.068478677811238</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4861684266984341</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.698523050213232</v>
+        <v>-4.506431185935755</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9472789049305446</v>
+        <v>1.024115650641536</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4861684266984341</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.901549627756466</v>
+        <v>-4.709457763478988</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8691996591331568</v>
+        <v>0.9460364048441479</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6891950042416675</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.743624028821173</v>
+        <v>-4.551532164543695</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9425422851394063</v>
+        <v>1.019379030850397</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6891950042416675</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.891945282632301</v>
+        <v>-4.699853418354824</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8781600541888153</v>
+        <v>0.9549967998998063</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6891950042416675</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.893128367283362</v>
+        <v>-4.701036503005884</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8694625957729165</v>
+        <v>0.9462993414839076</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.694838052708179</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.770000660289279</v>
+        <v>-4.577908796011801</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9192655516036514</v>
+        <v>0.9961022973146423</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.694838052708179</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.677190178838419</v>
+        <v>-4.485098314560942</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8856624360753609</v>
+        <v>0.962499181786352</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6020275712573196</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.628627126617389</v>
+        <v>-4.436535262339912</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9069611328883735</v>
+        <v>0.9837978785993646</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.5534645190362895</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.515955908381139</v>
+        <v>-4.323864044103662</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9471053286945967</v>
+        <v>1.023942074405588</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.4407933008000393</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.403578907198466</v>
+        <v>-4.211487042920989</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9975474249983332</v>
+        <v>1.074384170709324</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.4407933008000393</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.601813476085197</v>
+        <v>-4.409721611807719</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9297507992121798</v>
+        <v>1.006587544923171</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.6390278696867698</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.684814757110476</v>
+        <v>-4.492722892832998</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7349060068027216</v>
+        <v>0.8117427525137126</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.6575987542139436</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.338732593535068</v>
+        <v>3.824074205933332</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.689397606983304</v>
+        <v>-4.333528620776422</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8532225275727958</v>
+        <v>0.9955701220555488</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.6575987542139436</v>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-60.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.1%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-689.5%</t>
+          <t>-708.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.8%</t>
+          <t>439.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.9%</t>
+          <t>-630.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-276.2%</t>
+          <t>-283.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-42.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-67.0%</t>
+          <t>-131.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.7%</t>
+          <t>-290.9%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.5%</t>
+          <t>-163.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,27 +1471,27 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-212.5%</t>
+          <t>-195.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1952"/>
+  <dimension ref="A1:G1953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.601952958808613</v>
+        <v>-3.79404482308609</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.696952929915053</v>
+        <v>1.620116184204063</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4935892642914559</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.945635732035276</v>
+        <v>-4.137727596312753</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.561248944079004</v>
+        <v>1.484412198368014</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.601495316318674</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.303286082273624</v>
+        <v>-4.495377946551101</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.414294862639923</v>
+        <v>1.337458116928932</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.9591456665570222</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.612520185269675</v>
+        <v>-4.804612049547152</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.292374148141762</v>
+        <v>1.215537402430771</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.9591456665570222</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.044325978419463</v>
+        <v>-5.236417842696939</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.105984718349251</v>
+        <v>1.029147972638261</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.095563162998289</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.279019972552015</v>
+        <v>-5.471111836829492</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.000391895698321</v>
+        <v>0.9235551499873305</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.089226895769034</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.614682619782467</v>
+        <v>-5.806774484059944</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8647074284621055</v>
+        <v>0.7878706827511146</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.089226895769034</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.978308864682781</v>
+        <v>-6.170400728960257</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7257444907362216</v>
+        <v>0.6489077450252307</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.18744853263616</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.343436247321527</v>
+        <v>-6.535528111599004</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5789480526865542</v>
+        <v>0.5021113069755638</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.483759316935172</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.752025024502206</v>
+        <v>-6.944116888779682</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4142740858290419</v>
+        <v>0.3374373401180515</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.892348094115851</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.1650075086433</v>
+        <v>-7.357099372920776</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2442665246440647</v>
+        <v>0.1674297789330748</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.892348094115851</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.581399382930297</v>
+        <v>-7.773491247207773</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.07570382553814348</v>
+        <v>-0.001132920172846941</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.892348094115851</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.958076393460142</v>
+        <v>-8.150168257737617</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0647082880051153</v>
+        <v>-0.1415450337161053</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.892348094115851</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.30395121544495</v>
+        <v>-8.496043079722426</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2069586516533435</v>
+        <v>-0.2837953973643339</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.892348094115851</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.466093485908043</v>
+        <v>-8.658185350185519</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.27341063978358</v>
+        <v>-0.3502473854945705</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.892348094115851</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.762754827718242</v>
+        <v>-8.954846691995717</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3882962005784512</v>
+        <v>-0.4651329462894416</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.961091229849729</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.196103935828477</v>
+        <v>-9.388195800105953</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5656621483569482</v>
+        <v>-0.6424988940679386</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.961091229849729</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.579105324571108</v>
+        <v>-9.771197188848584</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7189648051755846</v>
+        <v>-0.795801550886575</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.961091229849729</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.736504204784229</v>
+        <v>-9.928596069061705</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7793528412894029</v>
+        <v>-0.8561895870003933</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.11849011006285</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.09603452728823</v>
+        <v>-10.28812639156571</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9178146669929532</v>
+        <v>-0.9946514127039441</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.11849011006285</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.42243455595324</v>
+        <v>-10.61452642023072</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.040458658501781</v>
+        <v>-1.117295404212772</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.444890138727863</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.64158352402744</v>
+        <v>-10.83367538830492</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.125076495109691</v>
+        <v>-1.201913240820681</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.664039106802061</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.63789259907103</v>
+        <v>-10.82998446334851</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.123600125127127</v>
+        <v>-1.200436870838117</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.664039106802061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.84215077440089</v>
+        <v>-11.03424263867837</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.19979019814043</v>
+        <v>-1.27662694385142</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.79167805141605</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.06018854603207</v>
+        <v>-11.25228041030955</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.282522752308465</v>
+        <v>-1.359359498019455</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.966448819511949</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.98671871436462</v>
+        <v>-11.1788105786421</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.237763118148064</v>
+        <v>-1.314599863859055</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.8929789878445</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16184313175117</v>
+        <v>-11.35393499602864</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.293257664355165</v>
+        <v>-1.370094410066155</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.068103405231044</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.39629522576566</v>
+        <v>-11.58838709004313</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.394257666862556</v>
+        <v>-1.471094412573547</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.068103405231044</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.68409907030289</v>
+        <v>-11.87619093458037</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.516051395451429</v>
+        <v>-1.592888141162419</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.355907249768282</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.91392351746672</v>
+        <v>-12.10601538174419</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.606865384478402</v>
+        <v>-1.683702130189393</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.518554786838443</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.14595243720298</v>
+        <v>-12.33804430148046</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.696983223743792</v>
+        <v>-1.773819969454782</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.580567484026866</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.09393692323417</v>
+        <v>-12.28602878751164</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.672186682469866</v>
+        <v>-1.749023428180856</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.580567484026866</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.23560876495829</v>
+        <v>-12.42770062923576</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.730330646058256</v>
+        <v>-1.807167391769246</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.580567484026866</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.18601792053345</v>
+        <v>-12.37810978481093</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.69544089812345</v>
+        <v>-1.77227764383444</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.530976639602032</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.98686581329635</v>
+        <v>-12.17895767757383</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.628831188875294</v>
+        <v>-1.705667934586284</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.365654113652219</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.76102066057694</v>
+        <v>-11.95311252485442</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.52891405475132</v>
+        <v>-1.60575080046231</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.323727438065055</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.63644200423935</v>
+        <v>-11.82853386851683</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.477943447660224</v>
+        <v>-1.554780193371215</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.323727438065055</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68933729228364</v>
+        <v>-11.88142915656111</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.496467788715831</v>
+        <v>-1.573304534426821</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.318772091976609</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.40542856135489</v>
+        <v>-11.59752042563236</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.377170592105695</v>
+        <v>-1.454007337816686</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.318772091976609</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.29000763721679</v>
+        <v>-11.48209950149427</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.340739484844322</v>
+        <v>-1.417576230555312</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.203351167838513</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.02617077001272</v>
+        <v>-11.2182626342902</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.245088219275602</v>
+        <v>-1.321924964986592</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.203351167838513</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.75892896914432</v>
+        <v>-10.9510208334218</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.140026059427616</v>
+        <v>-1.216862805138607</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.203351167838513</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.63562304066611</v>
+        <v>-10.82771490494358</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.091004003009789</v>
+        <v>-1.16784074872078</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.11393349671095</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61166949969015</v>
+        <v>-10.80376136396762</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.080754080473912</v>
+        <v>-1.157590826184903</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.089979955734993</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.34760956136735</v>
+        <v>-10.53970142564483</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.988390421306546</v>
+        <v>-1.065227167017536</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.825920017412197</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.640529937862514</v>
+        <v>-9.83262180213999</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.708345605564912</v>
+        <v>-0.7851823512759024</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.825920017412197</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.600345639496323</v>
+        <v>-9.792437503773799</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6919282623305945</v>
+        <v>-0.7687650080415849</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.785735719046006</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.520275843958519</v>
+        <v>-9.712367708235995</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6605335228947156</v>
+        <v>-0.737370268605706</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.705665923508202</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.286794621728919</v>
+        <v>-9.478886486006395</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5592166051650236</v>
+        <v>-0.636053350876014</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.472184701278603</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.107086091585046</v>
+        <v>-9.299177955862522</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4902254034204332</v>
+        <v>-0.5670621491314236</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.415013197115907</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.974810617954159</v>
+        <v>-9.166902482231635</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4419477272210512</v>
+        <v>-0.5187844729320417</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.282737723485021</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.784210943281005</v>
+        <v>-8.976302807558481</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3628927966641533</v>
+        <v>-0.4397295423751437</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.092138048811868</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.535211144597424</v>
+        <v>-8.7273030088749</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2503865359670621</v>
+        <v>-0.3272232816780525</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.092138048811868</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.640801134370529</v>
+        <v>-8.832892998648004</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4205984614755227</v>
+        <v>-0.4974352071865127</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.197728038584973</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.659536036489126</v>
+        <v>-8.851627900766601</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3795480804458751</v>
+        <v>-0.4563848261568655</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.197728038584973</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.511595995081526</v>
+        <v>-8.703687859359002</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4402509865710029</v>
+        <v>-0.5170877322819933</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.177407122676415</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.487367358692554</v>
+        <v>-8.67945922297003</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4392735182688918</v>
+        <v>-0.5161102639798822</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.153178486287443</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.443818951921862</v>
+        <v>-8.635910816199338</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4288147676557088</v>
+        <v>-0.5056515133666988</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.153178486287443</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.201670558468004</v>
+        <v>-8.39376242274548</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3174930558930225</v>
+        <v>-0.3943298016040124</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.153178486287443</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.138441186699657</v>
+        <v>-8.330533050977133</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2976691867264885</v>
+        <v>-0.3745059324374784</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.153178486287443</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.015150051882527</v>
+        <v>-8.207241916160003</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2508546387890593</v>
+        <v>-0.3276913845000498</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.029887351470312</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.994000852979084</v>
+        <v>-8.18609271725656</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.234693980990357</v>
+        <v>-0.3115307267013474</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.008738152566869</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.750235410995639</v>
+        <v>-7.942327275273116</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1414070958499285</v>
+        <v>-0.2182438415609194</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.008738152566869</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.486207343802379</v>
+        <v>-7.678299208079856</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03367155505260833</v>
+        <v>-0.1105083007635992</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.806872753750915</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.236356949853304</v>
+        <v>-7.428448814130782</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.05901067751072375</v>
+        <v>-0.01782606820026755</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.806872753750915</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.060464857385872</v>
+        <v>-7.25255672166335</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1329666380183454</v>
+        <v>0.0561298923073541</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.806872753750915</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.889018394363409</v>
+        <v>-7.081110258640886</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2148727292818844</v>
+        <v>0.1380359835708931</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.635426290728452</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.663985394694586</v>
+        <v>-6.856077258972063</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3039064067657105</v>
+        <v>0.2270696610547196</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.410393291059629</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.449351017058179</v>
+        <v>-6.641442881335657</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3944549588745905</v>
+        <v>0.3176182131635996</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.195758913423222</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.182750660083827</v>
+        <v>-6.374842524361305</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4822893604481266</v>
+        <v>0.4054526147371358</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.195758913423222</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.942320163278967</v>
+        <v>-6.134412027556444</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5802046357949484</v>
+        <v>0.5033678900839571</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9553284166183622</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.699529355629521</v>
+        <v>-5.891621219906999</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6812502726895469</v>
+        <v>0.6044135269785555</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9553284166183622</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.583589506004336</v>
+        <v>-5.775681370281814</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7283047964569609</v>
+        <v>0.65146805074597</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8785066856022383</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.340933917581173</v>
+        <v>-5.533025781858651</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8223651030462196</v>
+        <v>0.7455283573352283</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8785066856022383</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.120913119544163</v>
+        <v>-5.31300498382164</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9119524592716379</v>
+        <v>0.8351157135606466</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7372868405342581</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.921664489639354</v>
+        <v>-5.113756353916831</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.007546094035385</v>
+        <v>0.9307093483243936</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7372868405342581</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.762149386119984</v>
+        <v>-4.954241250397462</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.072497979883435</v>
+        <v>0.9956612341724436</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5777717370148882</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.617477241020246</v>
+        <v>-4.809569105297724</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.140454940484769</v>
+        <v>1.063618194773778</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.4330995919151507</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.677352068377939</v>
+        <v>-4.869443932655416</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.102542500943118</v>
+        <v>1.025705755232127</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4929744192728429</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.590552570598931</v>
+        <v>-4.782644434876408</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.159662793377288</v>
+        <v>1.082826047666297</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4929744192728429</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.593022277060737</v>
+        <v>-4.785114141338214</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.158747312165977</v>
+        <v>1.081910566454986</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.495444125734649</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.661392463384747</v>
+        <v>-4.853484327662224</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.142406160111075</v>
+        <v>1.065569414400084</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4861684266984341</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978373</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.53997603375827</v>
+        <v>-4.732067898035748</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.181409440593557</v>
+        <v>1.104572694882566</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4861684266984341</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.570969193086976</v>
+        <v>-4.763061057364453</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.993721741902462</v>
+        <v>0.9168849961914709</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4861684266984341</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.395494933294506</v>
+        <v>-4.587586797571984</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.068478677811238</v>
+        <v>0.9916419321002465</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4861684266984341</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.76502074769545</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.506431185935755</v>
+        <v>-4.698523050213232</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.024115650641536</v>
+        <v>0.9472789049305446</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4861684266984341</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.709457763478988</v>
+        <v>-4.901549627756466</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9460364048441479</v>
+        <v>0.8691996591331568</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6891950042416675</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.551532164543695</v>
+        <v>-4.743624028821173</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.019379030850397</v>
+        <v>0.9425422851394063</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6891950042416675</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.699853418354824</v>
+        <v>-4.891945282632301</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9549967998998063</v>
+        <v>0.8781600541888153</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6891950042416675</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.701036503005884</v>
+        <v>-4.893128367283362</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9462993414839076</v>
+        <v>0.8694625957729165</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.694838052708179</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.577908796011801</v>
+        <v>-4.770000660289279</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9961022973146423</v>
+        <v>0.9192655516036514</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.694838052708179</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.485098314560942</v>
+        <v>-4.677190178838419</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.962499181786352</v>
+        <v>0.8856624360753609</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6020275712573196</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.436535262339912</v>
+        <v>-4.628627126617389</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9837978785993646</v>
+        <v>0.9069611328883735</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.5534645190362895</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.323864044103662</v>
+        <v>-4.515955908381139</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.023942074405588</v>
+        <v>0.9471053286945967</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.4407933008000393</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.211487042920989</v>
+        <v>-4.403578907198466</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.074384170709324</v>
+        <v>0.9975474249983332</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.4407933008000393</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.409721611807719</v>
+        <v>-4.601813476085197</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.006587544923171</v>
+        <v>0.9297507992121798</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.6390278696867698</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.492722892832998</v>
+        <v>-4.684814757110476</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8117427525137126</v>
+        <v>0.7349060068027216</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.6575987542139436</v>
@@ -46441,22 +46441,45 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.824074205933332</v>
+        <v>3.682712735199276</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.333528620776422</v>
+        <v>-4.689397606983304</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9955701220555488</v>
+        <v>0.8532225275727958</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.6575987542139436</v>
       </c>
       <c r="G1952" t="n">
         <v>2.334778742151499</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="2" t="n">
+        <v>45415</v>
+      </c>
+      <c r="B1953" t="n">
+        <v>3.351850197670161</v>
+      </c>
+      <c r="C1953" t="n">
+        <v>2.510887956291612</v>
+      </c>
+      <c r="D1953" t="n">
+        <v>-4.689397606983304</v>
+      </c>
+      <c r="E1953" t="n">
+        <v>0.8532225275727958</v>
+      </c>
+      <c r="F1953" t="n">
+        <v>-0.6575987542139436</v>
+      </c>
+      <c r="G1953" t="n">
+        <v>2.50395175327798</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-60.5%</t>
+          <t>-39.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>115.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>135.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-708.7%</t>
+          <t>-690.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-55.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.5%</t>
+          <t>444.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.5%</t>
+          <t>-611.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-276.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.9%</t>
+          <t>-283.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.7%</t>
+          <t>-159.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-195.6%</t>
+          <t>-174.3%</t>
         </is>
       </c>
     </row>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.79404482308609</v>
+        <v>-3.608204173207077</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.620116184204063</v>
+        <v>1.694452444155668</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4935892642914559</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.137727596312753</v>
+        <v>-3.95188694643374</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.484412198368014</v>
+        <v>1.558748458319619</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.601495316318674</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.495377946551101</v>
+        <v>-4.309537296672088</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.337458116928932</v>
+        <v>1.411794376880537</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.9591456665570222</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.804612049547152</v>
+        <v>-4.618771399668139</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.215537402430771</v>
+        <v>1.289873662382377</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.9591456665570222</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.236417842696939</v>
+        <v>-5.050577192817927</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.029147972638261</v>
+        <v>1.103484232589866</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.095563162998289</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.471111836829492</v>
+        <v>-5.285271186950479</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9235551499873305</v>
+        <v>0.9978914099389358</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.089226895769034</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.806774484059944</v>
+        <v>-5.620933834180931</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7878706827511146</v>
+        <v>0.8622069427027199</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.089226895769034</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.170400728960257</v>
+        <v>-5.984560079081245</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6489077450252307</v>
+        <v>0.7232440049768361</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.18744853263616</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.535528111599004</v>
+        <v>-6.349687461719991</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5021113069755638</v>
+        <v>0.5764475669271687</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.483759316935172</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.944116888779682</v>
+        <v>-6.75827623890067</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3374373401180515</v>
+        <v>0.4117736000696564</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.892348094115851</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.357099372920776</v>
+        <v>-7.171258723041764</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1674297789330748</v>
+        <v>0.2417660388846792</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.892348094115851</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.773491247207773</v>
+        <v>-7.587650597328762</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.001132920172846941</v>
+        <v>0.07320333977875748</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.892348094115851</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.150168257737617</v>
+        <v>-7.964327607858606</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1415450337161053</v>
+        <v>-0.0672087737645013</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.892348094115851</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.496043079722426</v>
+        <v>-8.310202429843415</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2837953973643339</v>
+        <v>-0.2094591374127295</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.892348094115851</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.658185350185519</v>
+        <v>-8.472344700306508</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3502473854945705</v>
+        <v>-0.2759111255429656</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.892348094115851</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.954846691995717</v>
+        <v>-8.769006042116706</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4651329462894416</v>
+        <v>-0.3907966863378367</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.961091229849729</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.388195800105953</v>
+        <v>-9.202355150226941</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6424988940679386</v>
+        <v>-0.5681626341163337</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.961091229849729</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.771197188848584</v>
+        <v>-9.585356538969572</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.795801550886575</v>
+        <v>-0.7214652909349706</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.961091229849729</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.928596069061705</v>
+        <v>-9.742755419182693</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8561895870003933</v>
+        <v>-0.7818533270487884</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.11849011006285</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.28812639156571</v>
+        <v>-10.10228574168669</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9946514127039441</v>
+        <v>-0.9203151527523392</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.11849011006285</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.61452642023072</v>
+        <v>-10.42868577035171</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.117295404212772</v>
+        <v>-1.042959144261167</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.444890138727863</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.83367538830492</v>
+        <v>-10.6478347384259</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.201913240820681</v>
+        <v>-1.127576980869077</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.664039106802061</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.82998446334851</v>
+        <v>-10.64414381346949</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.200436870838117</v>
+        <v>-1.126100610886513</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.664039106802061</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.03424263867837</v>
+        <v>-10.84840198879936</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.27662694385142</v>
+        <v>-1.202290683899816</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.79167805141605</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.25228041030955</v>
+        <v>-11.06643976043054</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.359359498019455</v>
+        <v>-1.285023238067851</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.966448819511949</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.1788105786421</v>
+        <v>-10.99296992876309</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.314599863859055</v>
+        <v>-1.24026360390745</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.8929789878445</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.35393499602864</v>
+        <v>-11.16809434614963</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.370094410066155</v>
+        <v>-1.29575815011455</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.068103405231044</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.58838709004313</v>
+        <v>-11.40254644016412</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.471094412573547</v>
+        <v>-1.396758152621942</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.068103405231044</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.87619093458037</v>
+        <v>-11.69035028470136</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.592888141162419</v>
+        <v>-1.518551881210814</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.355907249768282</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.10601538174419</v>
+        <v>-11.92017473186518</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.683702130189393</v>
+        <v>-1.609365870237788</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.518554786838443</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.33804430148046</v>
+        <v>-12.15220365160144</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.773819969454782</v>
+        <v>-1.699483709503178</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.580567484026866</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.28602878751164</v>
+        <v>-12.10018813763263</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.749023428180856</v>
+        <v>-1.674687168229251</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.580567484026866</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.42770062923576</v>
+        <v>-12.24185997935675</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.807167391769246</v>
+        <v>-1.732831131817641</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.580567484026866</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.37810978481093</v>
+        <v>-12.19226913493192</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.77227764383444</v>
+        <v>-1.697941383882835</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.530976639602032</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.17895767757383</v>
+        <v>-11.99311702769482</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.705667934586284</v>
+        <v>-1.631331674634679</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.365654113652219</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.95311252485442</v>
+        <v>-11.76727187497541</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.60575080046231</v>
+        <v>-1.531414540510706</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.323727438065055</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.82853386851683</v>
+        <v>-11.64269321863781</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.554780193371215</v>
+        <v>-1.48044393341961</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.323727438065055</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.88142915656111</v>
+        <v>-11.6955885066821</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.573304534426821</v>
+        <v>-1.498968274475216</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.318772091976609</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.59752042563236</v>
+        <v>-11.41167977575335</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.454007337816686</v>
+        <v>-1.379671077865081</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.318772091976609</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.48209950149427</v>
+        <v>-11.29625885161526</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.417576230555312</v>
+        <v>-1.343239970603707</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.203351167838513</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.2182626342902</v>
+        <v>-11.03242198441119</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.321924964986592</v>
+        <v>-1.247588705034987</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.203351167838513</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9510208334218</v>
+        <v>-10.76518018354279</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.216862805138607</v>
+        <v>-1.142526545187002</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.203351167838513</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.82771490494358</v>
+        <v>-10.64187425506457</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.16784074872078</v>
+        <v>-1.093504488769175</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.11393349671095</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.80376136396762</v>
+        <v>-10.61792071408861</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.157590826184903</v>
+        <v>-1.083254566233298</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.089979955734993</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.53970142564483</v>
+        <v>-10.35386077576582</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.065227167017536</v>
+        <v>-0.990890907065932</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.825920017412197</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.83262180213999</v>
+        <v>-9.646781152260978</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7851823512759024</v>
+        <v>-0.7108460913242975</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.825920017412197</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.792437503773799</v>
+        <v>-9.606596853894787</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7687650080415849</v>
+        <v>-0.69442874808998</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.785735719046006</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.712367708235995</v>
+        <v>-9.526527058356983</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.737370268605706</v>
+        <v>-0.6630340086541011</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.705665923508202</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.478886486006395</v>
+        <v>-9.293045836127384</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.636053350876014</v>
+        <v>-0.5617170909244091</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.472184701278603</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.299177955862522</v>
+        <v>-9.11333730598351</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5670621491314236</v>
+        <v>-0.4927258891798187</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.415013197115907</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.166902482231635</v>
+        <v>-8.981061832352623</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5187844729320417</v>
+        <v>-0.4444482129804368</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.282737723485021</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.976302807558481</v>
+        <v>-8.790462157679469</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4397295423751437</v>
+        <v>-0.3653932824235389</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.092138048811868</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.7273030088749</v>
+        <v>-8.541462358995888</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3272232816780525</v>
+        <v>-0.2528870217264476</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.092138048811868</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.832892998648004</v>
+        <v>-8.647052348768993</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4974352071865127</v>
+        <v>-0.4230989472349083</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.197728038584973</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.851627900766601</v>
+        <v>-8.66578725088759</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4563848261568655</v>
+        <v>-0.3820485662052606</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.197728038584973</v>
@@ -45478,19 +45478,19 @@
         <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.966522116279655</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.703687859359002</v>
+        <v>-8.51784720947999</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5170877322819933</v>
+        <v>-0.4409731918260889</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.177407122676415</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.658299562169506</v>
+        <v>1.660077842673806</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.957808130026176</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.67945922297003</v>
+        <v>-8.493618573091018</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5161102639798822</v>
+        <v>-0.4399957235239782</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.153178486287443</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.664122757749412</v>
+        <v>1.665901038253711</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.950847517931083</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.635910816199338</v>
+        <v>-8.450070166320327</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5056515133666988</v>
+        <v>-0.4295369729107947</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.153178486287443</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.657162145654318</v>
+        <v>1.658940426158618</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.965309872312226</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.39376242274548</v>
+        <v>-8.207921772866468</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3943298016040124</v>
+        <v>-0.3182152611481084</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.153178486287443</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.671624500035461</v>
+        <v>1.673402780539761</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.959841992771421</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.330533050977133</v>
+        <v>-8.144692401098121</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3745059324374784</v>
+        <v>-0.2983913919815744</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.153178486287443</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.666156620494657</v>
+        <v>1.667934900998956</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.957340086781998</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.207241916160003</v>
+        <v>-8.021401266280991</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3276913845000498</v>
+        <v>-0.2515768440441453</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.029887351470312</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.737629395395512</v>
+        <v>1.739407675899811</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.965041065019324</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.18609271725656</v>
+        <v>-8.000252067377549</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3115307267013474</v>
+        <v>-0.2354161862454429</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.008738152566869</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.758019892974903</v>
+        <v>1.759798173479202</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.960821773366374</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.942327275273116</v>
+        <v>-7.756486625394104</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2182438415609194</v>
+        <v>-0.1421293011050144</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.008738152566869</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.753800601321953</v>
+        <v>1.755578881826253</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.96294608728639</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.678299208079856</v>
+        <v>-7.492458558200844</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1105083007635992</v>
+        <v>-0.03439376030769425</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.806872753750915</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.877044154531541</v>
+        <v>1.878822435035841</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.955688162270092</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.428448814130782</v>
+        <v>-7.242608164251769</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.01782606820026755</v>
+        <v>0.05828847225563782</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.806872753750915</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.869786229515244</v>
+        <v>1.871564510019543</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.959287285790741</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.25255672166335</v>
+        <v>-7.066716071784337</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.0561298923073541</v>
+        <v>0.132244432763259</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.806872753750915</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.873385353035892</v>
+        <v>1.875163633540192</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.972614791845295</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.081110258640886</v>
+        <v>-6.895269608761874</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1380359835708931</v>
+        <v>0.2141505240267985</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.635426290728452</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.989580736903924</v>
+        <v>1.991359017408224</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.971635269461592</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.856077258972063</v>
+        <v>-6.670236609093051</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2270696610547196</v>
+        <v>0.3031842015106245</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.410393291059629</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.123621014321515</v>
+        <v>2.125399294825814</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.976330070515909</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.641442881335657</v>
+        <v>-6.455602231456644</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3176182131635996</v>
+        <v>0.3937327536195045</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.195758913423222</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.257096441957676</v>
+        <v>2.258874722461976</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.957524329299705</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.374842524361305</v>
+        <v>-6.189001874482292</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4054526147371358</v>
+        <v>0.4815671551930407</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.195758913423222</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.238290700741472</v>
+        <v>2.240068981245772</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.959267405924582</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.134412027556444</v>
+        <v>-5.948571377677432</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5033678900839571</v>
+        <v>0.5794824305398625</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9553284166183622</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.384292075449265</v>
+        <v>2.386070355953565</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.963196719759402</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.891621219906999</v>
+        <v>-5.705780570027986</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6044135269785555</v>
+        <v>0.6805280674344609</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9553284166183622</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.388221389284086</v>
+        <v>2.389999669788385</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.963875303676742</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.775681370281814</v>
+        <v>-5.589840720402801</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.65146805074597</v>
+        <v>0.727582591201875</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8785066856022383</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.4349930118111</v>
+        <v>2.4367712923154</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.960873374896736</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.533025781858651</v>
+        <v>-5.347185131979638</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7455283573352283</v>
+        <v>0.8216428977911336</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8785066856022383</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.431991083031094</v>
+        <v>2.433769363535393</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.96245241190735</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.31300498382164</v>
+        <v>-5.127164333942628</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8351157135606466</v>
+        <v>0.911230254016552</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7372868405342581</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.518302027082496</v>
+        <v>2.520080307586795</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.978346594709173</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.113756353916831</v>
+        <v>-4.927915704037819</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9307093483243936</v>
+        <v>1.006823888780299</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7372868405342581</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.534196209884319</v>
+        <v>2.535974490388619</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.979492439149475</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.954241250397462</v>
+        <v>-4.768400600518449</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9956612341724436</v>
+        <v>1.071775774628348</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5777717370148882</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.631051116436243</v>
+        <v>2.632829396940542</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.989580541710915</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.809569105297724</v>
+        <v>-4.623728455418711</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.063618194773778</v>
+        <v>1.139732735229683</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.4330995919151507</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.727942506057525</v>
+        <v>2.729720786561825</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.973839752608041</v>
+        <v>2.975618033112341</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.869443932655416</v>
+        <v>-4.683603282776404</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.025705755232127</v>
+        <v>1.101820295688032</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4929744192728429</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.678055101044336</v>
+        <v>2.679833381548635</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>2.998018526434907</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.782644434876408</v>
+        <v>-4.596803784997396</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.082826047666297</v>
+        <v>1.158940588122202</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4929744192728429</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.700455594366902</v>
+        <v>2.702233874871201</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>2.998090927808319</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.785114141338214</v>
+        <v>-4.599273491459202</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.081910566454986</v>
+        <v>1.158025106910892</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.495444125734649</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.69904617186323</v>
+        <v>2.70082445236753</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.009097850283021</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.853484327662224</v>
+        <v>-4.667643677783212</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.065569414400084</v>
+        <v>1.141683954855989</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4861684266984341</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.715618513759661</v>
+        <v>2.717396794263961</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>2.999534558914912</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.732067898035748</v>
+        <v>-4.546227248156735</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.104572694882566</v>
+        <v>1.180687235338471</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4861684266984341</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.706055222391552</v>
+        <v>2.707833502895852</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.824244123955299</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.763061057364453</v>
+        <v>-4.577220407485441</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9168849961914709</v>
+        <v>0.9929995366473761</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4861684266984341</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.530764787431939</v>
+        <v>2.532543067936239</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.828811355947087</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.587586797571984</v>
+        <v>-4.401746147692971</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9916419321002465</v>
+        <v>1.067756472556152</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4861684266984341</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.535332019423727</v>
+        <v>2.537110299928027</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502074769545</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.827044549329585</v>
+        <v>2.828822829833884</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.698523050213232</v>
+        <v>-4.51268240033422</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9472789049305446</v>
+        <v>1.023393445386449</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4861684266984341</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.535343493310525</v>
+        <v>2.537121773814824</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581296</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.83017593454949</v>
+        <v>2.83195421505379</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.901549627756466</v>
+        <v>-4.715708977877453</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8691996591331568</v>
+        <v>0.9453141995890619</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6891950042416675</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.41665893200449</v>
+        <v>2.41843721250879</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734165</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.840348320981623</v>
+        <v>2.842126601485922</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.743624028821173</v>
+        <v>-4.55778337894216</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9425422851394063</v>
+        <v>1.018656825595311</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6891950042416675</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.426831318436622</v>
+        <v>2.428609598940922</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212301</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.835294591555483</v>
+        <v>2.837072872059783</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.891945282632301</v>
+        <v>-4.706104632753289</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8781600541888153</v>
+        <v>0.9542745946447202</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6891950042416675</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.421777589010483</v>
+        <v>2.423555869514782</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786049</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.827070367000009</v>
+        <v>2.828848647504308</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.893128367283362</v>
+        <v>-4.707287717404349</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8694625957729165</v>
+        <v>0.9455771362288217</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.694838052708179</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.410167535375102</v>
+        <v>2.411945815879401</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273194</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.82762224003311</v>
+        <v>2.82940052053741</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.770000660289279</v>
+        <v>-4.584160010410266</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9192655516036514</v>
+        <v>0.9953800920595564</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.694838052708179</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.410719408408203</v>
+        <v>2.412497688912503</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279503</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.756894931924476</v>
+        <v>2.758673212428775</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.677190178838419</v>
+        <v>-4.491349528959407</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8856624360753609</v>
+        <v>0.9617769765312658</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6020275712573196</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.395678389170084</v>
+        <v>2.397456669674384</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030431</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.758768407849077</v>
+        <v>2.760546688353376</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.628627126617389</v>
+        <v>-4.442786476738377</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9069611328883735</v>
+        <v>0.9830756733442787</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.5534645190362895</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.426689696427303</v>
+        <v>2.428467976931603</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942743</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.7538441163608</v>
+        <v>2.755622396865099</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.515955908381139</v>
+        <v>-4.330115258502127</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9471053286945967</v>
+        <v>1.023219869150502</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.4407933008000393</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.489368135880776</v>
+        <v>2.491146416385076</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268541</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.759335412191467</v>
+        <v>2.761113692695766</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.403578907198466</v>
+        <v>-4.217738257319454</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9975474249983332</v>
+        <v>1.073661965454238</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.4407933008000393</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.494859431711443</v>
+        <v>2.496637712215743</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968866</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.770832613960006</v>
+        <v>2.772610894464306</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.601813476085197</v>
+        <v>-4.415972826206184</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9297507992121798</v>
+        <v>1.005865339668085</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.6390278696867698</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.387415892147944</v>
+        <v>2.389194172652244</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175327</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.609188333960659</v>
+        <v>2.610966614464959</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.684814757110476</v>
+        <v>-4.498974107231463</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7349060068027216</v>
+        <v>0.8110205472586265</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.6575987542139436</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.214629081432293</v>
+        <v>2.216407361936593</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199276</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.729337994679865</v>
+        <v>2.731116275184164</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.689397606983304</v>
+        <v>-4.503556957104291</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8532225275727958</v>
+        <v>0.929337068028701</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.6575987542139436</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.334778742151499</v>
+        <v>2.336557022655799</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.351850197670161</v>
+        <v>3.750915674568301</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.510887956291612</v>
+        <v>2.724241815992405</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.689397606983304</v>
+        <v>-4.503556957104291</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8532225275727958</v>
+        <v>0.929337068028701</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.6575987542139436</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.50395175327798</v>
+        <v>2.717305612978773</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-39.2%</t>
+          <t>-57.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-80.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.0%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.0%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-690.1%</t>
+          <t>-708.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.8%</t>
+          <t>440.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.9%</t>
+          <t>-626.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-276.4%</t>
+          <t>-283.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-126.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.3%</t>
+          <t>-289.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.8%</t>
+          <t>-163.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-289.8%</t>
+          <t>-286.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-174.3%</t>
+          <t>-192.9%</t>
         </is>
       </c>
     </row>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.608204173207077</v>
+        <v>-3.79404482308609</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.694452444155668</v>
+        <v>1.620116184204063</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4935892642914559</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.95188694643374</v>
+        <v>-4.137727596312753</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.558748458319619</v>
+        <v>1.484412198368014</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.601495316318674</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.309537296672088</v>
+        <v>-4.495377946551101</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.411794376880537</v>
+        <v>1.337458116928932</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.9591456665570222</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.618771399668139</v>
+        <v>-4.804612049547152</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.289873662382377</v>
+        <v>1.215537402430771</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.9591456665570222</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.050577192817927</v>
+        <v>-5.236417842696939</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.103484232589866</v>
+        <v>1.029147972638261</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.095563162998289</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.285271186950479</v>
+        <v>-5.471111836829492</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9978914099389358</v>
+        <v>0.9235551499873305</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.089226895769034</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.620933834180931</v>
+        <v>-5.806774484059944</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8622069427027199</v>
+        <v>0.7878706827511146</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.089226895769034</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.984560079081245</v>
+        <v>-6.170400728960257</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7232440049768361</v>
+        <v>0.6489077450252307</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.18744853263616</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.349687461719991</v>
+        <v>-6.535528111599004</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5764475669271687</v>
+        <v>0.5021113069755638</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.483759316935172</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.75827623890067</v>
+        <v>-6.944116888779682</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4117736000696564</v>
+        <v>0.3374373401180515</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.892348094115851</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.171258723041764</v>
+        <v>-7.357099372920776</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2417660388846792</v>
+        <v>0.1674297789330748</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.892348094115851</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.587650597328762</v>
+        <v>-7.773491247207773</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.07320333977875748</v>
+        <v>-0.001132920172846941</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.892348094115851</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.964327607858606</v>
+        <v>-8.150168257737617</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0672087737645013</v>
+        <v>-0.1415450337161053</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.892348094115851</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.310202429843415</v>
+        <v>-8.496043079722426</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2094591374127295</v>
+        <v>-0.2837953973643339</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.892348094115851</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.472344700306508</v>
+        <v>-8.658185350185519</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2759111255429656</v>
+        <v>-0.3502473854945705</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.892348094115851</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.769006042116706</v>
+        <v>-8.954846691995717</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3907966863378367</v>
+        <v>-0.4651329462894416</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.961091229849729</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.202355150226941</v>
+        <v>-9.388195800105953</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5681626341163337</v>
+        <v>-0.6424988940679386</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.961091229849729</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.585356538969572</v>
+        <v>-9.771197188848584</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7214652909349706</v>
+        <v>-0.795801550886575</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.961091229849729</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.742755419182693</v>
+        <v>-9.928596069061705</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7818533270487884</v>
+        <v>-0.8561895870003933</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.11849011006285</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.10228574168669</v>
+        <v>-10.28812639156571</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9203151527523392</v>
+        <v>-0.9946514127039441</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.11849011006285</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.42868577035171</v>
+        <v>-10.61452642023072</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.042959144261167</v>
+        <v>-1.117295404212772</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.444890138727863</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.6478347384259</v>
+        <v>-10.83367538830492</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.127576980869077</v>
+        <v>-1.201913240820681</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.664039106802061</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.64414381346949</v>
+        <v>-10.82998446334851</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.126100610886513</v>
+        <v>-1.200436870838117</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.664039106802061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.84840198879936</v>
+        <v>-11.03424263867837</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.202290683899816</v>
+        <v>-1.27662694385142</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.79167805141605</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.06643976043054</v>
+        <v>-11.25228041030955</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.285023238067851</v>
+        <v>-1.359359498019455</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.966448819511949</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99296992876309</v>
+        <v>-11.1788105786421</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.24026360390745</v>
+        <v>-1.314599863859055</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.8929789878445</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16809434614963</v>
+        <v>-11.35393499602864</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.29575815011455</v>
+        <v>-1.370094410066155</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.068103405231044</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40254644016412</v>
+        <v>-11.58838709004313</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.396758152621942</v>
+        <v>-1.471094412573547</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.068103405231044</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.69035028470136</v>
+        <v>-11.87619093458037</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.518551881210814</v>
+        <v>-1.592888141162419</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.355907249768282</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.92017473186518</v>
+        <v>-12.10601538174419</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.609365870237788</v>
+        <v>-1.683702130189393</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.518554786838443</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.15220365160144</v>
+        <v>-12.33804430148046</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.699483709503178</v>
+        <v>-1.773819969454782</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.580567484026866</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.10018813763263</v>
+        <v>-12.28602878751164</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.674687168229251</v>
+        <v>-1.749023428180856</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.580567484026866</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24185997935675</v>
+        <v>-12.42770062923576</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.732831131817641</v>
+        <v>-1.807167391769246</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.580567484026866</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.19226913493192</v>
+        <v>-12.37810978481093</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.697941383882835</v>
+        <v>-1.77227764383444</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.530976639602032</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.99311702769482</v>
+        <v>-12.17895767757383</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.631331674634679</v>
+        <v>-1.705667934586284</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.365654113652219</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.76727187497541</v>
+        <v>-11.95311252485442</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.531414540510706</v>
+        <v>-1.60575080046231</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.323727438065055</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.64269321863781</v>
+        <v>-11.82853386851683</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.48044393341961</v>
+        <v>-1.554780193371215</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.323727438065055</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.6955885066821</v>
+        <v>-11.88142915656111</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.498968274475216</v>
+        <v>-1.573304534426821</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.318772091976609</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.41167977575335</v>
+        <v>-11.59752042563236</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.379671077865081</v>
+        <v>-1.454007337816686</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.318772091976609</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.29625885161526</v>
+        <v>-11.48209950149427</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.343239970603707</v>
+        <v>-1.417576230555312</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.203351167838513</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.03242198441119</v>
+        <v>-11.2182626342902</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.247588705034987</v>
+        <v>-1.321924964986592</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.203351167838513</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.76518018354279</v>
+        <v>-10.9510208334218</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.142526545187002</v>
+        <v>-1.216862805138607</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.203351167838513</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64187425506457</v>
+        <v>-10.82771490494358</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.093504488769175</v>
+        <v>-1.16784074872078</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.11393349671095</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61792071408861</v>
+        <v>-10.80376136396762</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083254566233298</v>
+        <v>-1.157590826184903</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.089979955734993</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35386077576582</v>
+        <v>-10.53970142564483</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.990890907065932</v>
+        <v>-1.065227167017536</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.825920017412197</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.646781152260978</v>
+        <v>-9.83262180213999</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7108460913242975</v>
+        <v>-0.7851823512759024</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.825920017412197</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.606596853894787</v>
+        <v>-9.792437503773799</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.69442874808998</v>
+        <v>-0.7687650080415849</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.785735719046006</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.526527058356983</v>
+        <v>-9.712367708235995</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6630340086541011</v>
+        <v>-0.737370268605706</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.705665923508202</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.293045836127384</v>
+        <v>-9.478886486006395</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5617170909244091</v>
+        <v>-0.636053350876014</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.472184701278603</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.11333730598351</v>
+        <v>-9.299177955862522</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4927258891798187</v>
+        <v>-0.5670621491314236</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.415013197115907</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.981061832352623</v>
+        <v>-9.166902482231635</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4444482129804368</v>
+        <v>-0.5187844729320417</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.282737723485021</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.790462157679469</v>
+        <v>-8.976302807558481</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3653932824235389</v>
+        <v>-0.4397295423751437</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.092138048811868</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.541462358995888</v>
+        <v>-8.7273030088749</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2528870217264476</v>
+        <v>-0.3272232816780525</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.092138048811868</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.647052348768993</v>
+        <v>-8.832892998648004</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4230989472349083</v>
+        <v>-0.4974352071865127</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.197728038584973</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.66578725088759</v>
+        <v>-8.851627900766601</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3820485662052606</v>
+        <v>-0.4563848261568655</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.197728038584973</v>
@@ -45478,19 +45478,19 @@
         <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.966522116279655</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.51784720947999</v>
+        <v>-8.695681825439518</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4409731918260889</v>
+        <v>-0.5138853187141996</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.177407122676415</v>
+        <v>-2.148000461965292</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.660077842673806</v>
+        <v>1.67594355859618</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.957808130026176</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.493618573091018</v>
+        <v>-8.671453189050546</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4399957235239782</v>
+        <v>-0.5129078504120885</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.12377182557632</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.665901038253711</v>
+        <v>1.681766754176085</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.950847517931083</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.450070166320327</v>
+        <v>-8.627904782279854</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4295369729107947</v>
+        <v>-0.5024490997989055</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.12377182557632</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.658940426158618</v>
+        <v>1.674806142080992</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.965309872312226</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.207921772866468</v>
+        <v>-8.385756388825996</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3182152611481084</v>
+        <v>-0.3911273880362192</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.12377182557632</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.673402780539761</v>
+        <v>1.689268496462135</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.959841992771421</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.144692401098121</v>
+        <v>-8.322527017057649</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2983913919815744</v>
+        <v>-0.3713035188696852</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.153178486287443</v>
+        <v>-2.12377182557632</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.667934900998956</v>
+        <v>1.68380061692133</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.957340086781998</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.021401266280991</v>
+        <v>-8.199235882240519</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2515768440441453</v>
+        <v>-0.324488970932256</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.029887351470312</v>
+        <v>-2.000480690759189</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.739407675899811</v>
+        <v>1.755273391822185</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.965041065019324</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.000252067377549</v>
+        <v>-8.178086683337074</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2354161862454429</v>
+        <v>-0.3083283131335532</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.008738152566869</v>
+        <v>-1.979331491855746</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.759798173479202</v>
+        <v>1.775663889401577</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.960821773366374</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.756486625394104</v>
+        <v>-7.93432124135363</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1421293011050144</v>
+        <v>-0.2150414279931248</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.008738152566869</v>
+        <v>-1.979331491855746</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.755578881826253</v>
+        <v>1.771444597748627</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.96294608728639</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.492458558200844</v>
+        <v>-7.670293174160371</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03439376030769425</v>
+        <v>-0.107305887195805</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.777466093039793</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.878822435035841</v>
+        <v>1.894688150958215</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.955688162270092</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.242608164251769</v>
+        <v>-7.420442780211296</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.05828847225563782</v>
+        <v>-0.01462365463247295</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.777466093039793</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.871564510019543</v>
+        <v>1.887430225941918</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.959287285790741</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.066716071784337</v>
+        <v>-7.244550687743864</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.132244432763259</v>
+        <v>0.05933230587514871</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.777466093039793</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.875163633540192</v>
+        <v>1.891029349462566</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.972614791845295</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.895269608761874</v>
+        <v>-7.0731042247214</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2141505240267985</v>
+        <v>0.1412383971386877</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.635426290728452</v>
+        <v>-1.606019630017329</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.991359017408224</v>
+        <v>2.007224733330598</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.971635269461592</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.670236609093051</v>
+        <v>-6.848071225052577</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3031842015106245</v>
+        <v>0.2302720746225138</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.410393291059629</v>
+        <v>-1.380986630348506</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.125399294825814</v>
+        <v>2.141265010748189</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.976330070515909</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.455602231456644</v>
+        <v>-6.633436847416171</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3937327536195045</v>
+        <v>0.3208206267313938</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.195758913423222</v>
+        <v>-1.1663522527121</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.258874722461976</v>
+        <v>2.27474043838435</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.957524329299705</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.189001874482292</v>
+        <v>-6.366836490441819</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4815671551930407</v>
+        <v>0.4086550283049299</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.195758913423222</v>
+        <v>-1.1663522527121</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.240068981245772</v>
+        <v>2.255934697168146</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.959267405924582</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.948571377677432</v>
+        <v>-6.126405993636959</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5794824305398625</v>
+        <v>0.5065703036517517</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9553284166183622</v>
+        <v>-0.9259217559072392</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.386070355953565</v>
+        <v>2.401936071875939</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.963196719759402</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.705780570027986</v>
+        <v>-5.883615185987513</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6805280674344609</v>
+        <v>0.6076159405463502</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9553284166183622</v>
+        <v>-0.9259217559072392</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.389999669788385</v>
+        <v>2.405865385710759</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.963875303676742</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.589840720402801</v>
+        <v>-5.767675336362328</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.727582591201875</v>
+        <v>0.6546704643137642</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8785066856022383</v>
+        <v>-0.8491000248911154</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.4367712923154</v>
+        <v>2.452637008237774</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.960873374896736</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.347185131979638</v>
+        <v>-5.525019747939165</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8216428977911336</v>
+        <v>0.7487307709030229</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8785066856022383</v>
+        <v>-0.8491000248911154</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.433769363535393</v>
+        <v>2.449635079457767</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96245241190735</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.127164333942628</v>
+        <v>-5.304998949902155</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.911230254016552</v>
+        <v>0.8383181271284412</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7372868405342581</v>
+        <v>-0.7078801798231351</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.520080307586795</v>
+        <v>2.535946023509169</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.978346594709173</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.927915704037819</v>
+        <v>-5.105750319997346</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.006823888780299</v>
+        <v>0.9339117618921882</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7372868405342581</v>
+        <v>-0.7078801798231351</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.535974490388619</v>
+        <v>2.551840206310993</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.979492439149475</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.768400600518449</v>
+        <v>-4.946235216477976</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.071775774628348</v>
+        <v>0.9988636477402379</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5777717370148882</v>
+        <v>-0.5483650763037652</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.632829396940542</v>
+        <v>2.648695112862916</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.989580541710915</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.623728455418711</v>
+        <v>-4.801563071378238</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.139732735229683</v>
+        <v>1.066820608341573</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4330995919151507</v>
+        <v>-0.4036929312040278</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.729720786561825</v>
+        <v>2.745586502484199</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.975618033112341</v>
+        <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.683603282776404</v>
+        <v>-4.861437898735931</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.101820295688032</v>
+        <v>1.028908168799922</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4929744192728429</v>
+        <v>-0.4635677585617199</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.679833381548635</v>
+        <v>2.695699097471009</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.998018526434907</v>
+        <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.596803784997396</v>
+        <v>-4.774638400956922</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.158940588122202</v>
+        <v>1.086028461234091</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4929744192728429</v>
+        <v>-0.4635677585617199</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.702233874871201</v>
+        <v>2.718099590793575</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.998090927808319</v>
+        <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.599273491459202</v>
+        <v>-4.777108107418728</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.158025106910892</v>
+        <v>1.085112980022781</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.495444125734649</v>
+        <v>-0.4660374650235261</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.70082445236753</v>
+        <v>2.716690168289904</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.009097850283021</v>
+        <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.667643677783212</v>
+        <v>-4.845478293742739</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.141683954855989</v>
+        <v>1.068771827967879</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.4567617659873111</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.717396794263961</v>
+        <v>2.733262510186335</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.999534558914912</v>
+        <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.546227248156735</v>
+        <v>-4.853742224484514</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.180687235338471</v>
+        <v>1.05590296430306</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.4567617659873111</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.707833502895852</v>
+        <v>2.723699218818226</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.824244123955299</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.577220407485441</v>
+        <v>-4.884735383813219</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9929995366473761</v>
+        <v>0.8682152656119644</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.4567617659873111</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.532543067936239</v>
+        <v>2.548408783858613</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.828811355947087</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.401746147692971</v>
+        <v>-4.709261124020751</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.067756472556152</v>
+        <v>0.9429722015207398</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.4567617659873111</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.537110299928027</v>
+        <v>2.552976015850401</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769545</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.828822829833884</v>
+        <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.51268240033422</v>
+        <v>-4.820197376662</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.023393445386449</v>
+        <v>0.8986091743510376</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.4567617659873111</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.537121773814824</v>
+        <v>2.552987489737198</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581296</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.83195421505379</v>
+        <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.715708977877453</v>
+        <v>-5.023223954205233</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9453141995890619</v>
+        <v>0.82052992855365</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6891950042416675</v>
+        <v>-0.6597883435305445</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.41843721250879</v>
+        <v>2.434302928431164</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734165</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.842126601485922</v>
+        <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.55778337894216</v>
+        <v>-4.86529835526994</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.018656825595311</v>
+        <v>0.8938725545598996</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6891950042416675</v>
+        <v>-0.6597883435305445</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.428609598940922</v>
+        <v>2.444475314863296</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212301</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.837072872059783</v>
+        <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.706104632753289</v>
+        <v>-5.013619609081069</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9542745946447202</v>
+        <v>0.8294903236093085</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6891950042416675</v>
+        <v>-0.6597883435305445</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.423555869514782</v>
+        <v>2.439421585437157</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786049</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.828848647504308</v>
+        <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.707287717404349</v>
+        <v>-5.014802693732129</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9455771362288217</v>
+        <v>0.8207928651934098</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.694838052708179</v>
+        <v>-0.665431391997056</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.411945815879401</v>
+        <v>2.427811531801775</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273194</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.82940052053741</v>
+        <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.584160010410266</v>
+        <v>-4.891674986738046</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9953800920595564</v>
+        <v>0.8705958210241445</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.694838052708179</v>
+        <v>-0.665431391997056</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.412497688912503</v>
+        <v>2.428363404834877</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279503</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.758673212428775</v>
+        <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.491349528959407</v>
+        <v>-4.798864505287186</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9617769765312658</v>
+        <v>0.8369927054958539</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6020275712573196</v>
+        <v>-0.5726209105461967</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.397456669674384</v>
+        <v>2.413322385596758</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030431</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.760546688353376</v>
+        <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.442786476738377</v>
+        <v>-4.750301453066156</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9830756733442787</v>
+        <v>0.8582914023088668</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5534645190362895</v>
+        <v>-0.5240578583251665</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.428467976931603</v>
+        <v>2.444333692853977</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942743</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.755622396865099</v>
+        <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.330115258502127</v>
+        <v>-4.637630234829906</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.023219869150502</v>
+        <v>0.8984355981150898</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4407933008000393</v>
+        <v>-0.4113866400889163</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.491146416385076</v>
+        <v>2.50701213230745</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268541</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.761113692695766</v>
+        <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.217738257319454</v>
+        <v>-4.525253233647233</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.073661965454238</v>
+        <v>0.9488776944188262</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4407933008000393</v>
+        <v>-0.4113866400889163</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.496637712215743</v>
+        <v>2.512503428138118</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968866</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.772610894464306</v>
+        <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.415972826206184</v>
+        <v>-4.723487802533964</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.005865339668085</v>
+        <v>0.8810810686326729</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6390278696867698</v>
+        <v>-0.6096212089756469</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.389194172652244</v>
+        <v>2.405059888574618</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175327</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.610966614464959</v>
+        <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.498974107231463</v>
+        <v>-4.806489083559243</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8110205472586265</v>
+        <v>0.6862362762232146</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6575987542139436</v>
+        <v>-0.6281920935028207</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.216407361936593</v>
+        <v>2.232273077858967</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199276</v>
+        <v>3.682712735199273</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.731116275184164</v>
+        <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.503556957104291</v>
+        <v>-4.647294811502666</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.929337068028701</v>
+        <v>0.870063645765051</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6575987542139436</v>
+        <v>-0.6281920935028207</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.336557022655799</v>
+        <v>2.352422738578173</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.750915674568301</v>
+        <v>3.383035908391638</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.724241815992405</v>
+        <v>2.537840637876454</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.503556957104291</v>
+        <v>-4.647294811502666</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.929337068028701</v>
+        <v>0.870063645765051</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6575987542139436</v>
+        <v>-0.6281920935028207</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.717305612978773</v>
+        <v>2.530904434862822</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-626.3%</t>
+          <t>-626.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-126.3%</t>
+          <t>-132.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-289.2%</t>
+          <t>-289.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.5%</t>
+          <t>-163.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-286.8%</t>
+          <t>-289.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.695681825439518</v>
+        <v>-8.703687859359002</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5138853187141996</v>
+        <v>-0.5170877322819933</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.148000461965292</v>
+        <v>-2.177407122676415</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.67594355859618</v>
+        <v>1.658299562169506</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.671453189050546</v>
+        <v>-8.67945922297003</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5129078504120885</v>
+        <v>-0.5161102639798822</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.12377182557632</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.681766754176085</v>
+        <v>1.664122757749412</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.627904782279854</v>
+        <v>-8.635910816199338</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5024490997989055</v>
+        <v>-0.5056515133666988</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.12377182557632</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.674806142080992</v>
+        <v>1.657162145654318</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.385756388825996</v>
+        <v>-8.39376242274548</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3911273880362192</v>
+        <v>-0.3943298016040124</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.12377182557632</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.689268496462135</v>
+        <v>1.671624500035461</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.322527017057649</v>
+        <v>-8.330533050977133</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3713035188696852</v>
+        <v>-0.3745059324374784</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.12377182557632</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.68380061692133</v>
+        <v>1.666156620494657</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.199235882240519</v>
+        <v>-8.207241916160003</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.324488970932256</v>
+        <v>-0.3276913845000498</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.000480690759189</v>
+        <v>-2.029887351470312</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.755273391822185</v>
+        <v>1.737629395395512</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.178086683337074</v>
+        <v>-8.18609271725656</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3083283131335532</v>
+        <v>-0.3115307267013474</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.979331491855746</v>
+        <v>-2.008738152566869</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.775663889401577</v>
+        <v>1.758019892974903</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.93432124135363</v>
+        <v>-7.942327275273116</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2150414279931248</v>
+        <v>-0.2182438415609194</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.979331491855746</v>
+        <v>-2.008738152566869</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.771444597748627</v>
+        <v>1.753800601321953</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.670293174160371</v>
+        <v>-7.678299208079856</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.107305887195805</v>
+        <v>-0.1105083007635992</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.777466093039793</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.894688150958215</v>
+        <v>1.877044154531541</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.420442780211296</v>
+        <v>-7.428448814130782</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.01462365463247295</v>
+        <v>-0.01782606820026755</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.777466093039793</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.887430225941918</v>
+        <v>1.869786229515244</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.244550687743864</v>
+        <v>-7.25255672166335</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.05933230587514871</v>
+        <v>0.0561298923073541</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.777466093039793</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.891029349462566</v>
+        <v>1.873385353035892</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.0731042247214</v>
+        <v>-7.081110258640886</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1412383971386877</v>
+        <v>0.1380359835708931</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.606019630017329</v>
+        <v>-1.635426290728452</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.007224733330598</v>
+        <v>1.989580736903924</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.848071225052577</v>
+        <v>-6.856077258972063</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2302720746225138</v>
+        <v>0.2270696610547196</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.380986630348506</v>
+        <v>-1.410393291059629</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.141265010748189</v>
+        <v>2.123621014321515</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.633436847416171</v>
+        <v>-6.641442881335657</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3208206267313938</v>
+        <v>0.3176182131635996</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.1663522527121</v>
+        <v>-1.195758913423222</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.27474043838435</v>
+        <v>2.257096441957676</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.366836490441819</v>
+        <v>-6.374842524361305</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4086550283049299</v>
+        <v>0.4054526147371358</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.1663522527121</v>
+        <v>-1.195758913423222</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.255934697168146</v>
+        <v>2.238290700741472</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.126405993636959</v>
+        <v>-6.134412027556444</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5065703036517517</v>
+        <v>0.5033678900839571</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9259217559072392</v>
+        <v>-0.9553284166183622</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.401936071875939</v>
+        <v>2.384292075449265</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.883615185987513</v>
+        <v>-5.891621219906999</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6076159405463502</v>
+        <v>0.6044135269785555</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9259217559072392</v>
+        <v>-0.9553284166183622</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.405865385710759</v>
+        <v>2.388221389284086</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.767675336362328</v>
+        <v>-5.775681370281814</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6546704643137642</v>
+        <v>0.65146805074597</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8491000248911154</v>
+        <v>-0.8785066856022383</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.452637008237774</v>
+        <v>2.4349930118111</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.525019747939165</v>
+        <v>-5.533025781858651</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7487307709030229</v>
+        <v>0.7455283573352283</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8491000248911154</v>
+        <v>-0.8785066856022383</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.449635079457767</v>
+        <v>2.431991083031094</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.304998949902155</v>
+        <v>-5.31300498382164</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8383181271284412</v>
+        <v>0.8351157135606466</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7078801798231351</v>
+        <v>-0.7372868405342581</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.535946023509169</v>
+        <v>2.518302027082496</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.105750319997346</v>
+        <v>-5.113756353916831</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9339117618921882</v>
+        <v>0.9307093483243936</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7078801798231351</v>
+        <v>-0.7372868405342581</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.551840206310993</v>
+        <v>2.534196209884319</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.946235216477976</v>
+        <v>-4.954241250397462</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9988636477402379</v>
+        <v>0.9956612341724436</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5483650763037652</v>
+        <v>-0.5777717370148882</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.648695112862916</v>
+        <v>2.631051116436243</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.801563071378238</v>
+        <v>-4.809569105297724</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.066820608341573</v>
+        <v>1.063618194773778</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4036929312040278</v>
+        <v>-0.4330995919151507</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.745586502484199</v>
+        <v>2.727942506057525</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.861437898735931</v>
+        <v>-4.869443932655416</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.028908168799922</v>
+        <v>1.025705755232127</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4635677585617199</v>
+        <v>-0.4929744192728429</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.695699097471009</v>
+        <v>2.678055101044336</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.774638400956922</v>
+        <v>-4.782644434876408</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.086028461234091</v>
+        <v>1.082826047666297</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4635677585617199</v>
+        <v>-0.4929744192728429</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.718099590793575</v>
+        <v>2.700455594366902</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.777108107418728</v>
+        <v>-4.785114141338214</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.085112980022781</v>
+        <v>1.081910566454986</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4660374650235261</v>
+        <v>-0.495444125734649</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.716690168289904</v>
+        <v>2.69904617186323</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.845478293742739</v>
+        <v>-4.853484327662224</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.068771827967879</v>
+        <v>1.065569414400084</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4567617659873111</v>
+        <v>-0.4861684266984341</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.733262510186335</v>
+        <v>2.715618513759661</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.853742224484514</v>
+        <v>-4.857958833236443</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.05590296430306</v>
+        <v>1.054216320802288</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4567617659873111</v>
+        <v>-0.4861684266984341</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.723699218818226</v>
+        <v>2.706055222391552</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.884735383813219</v>
+        <v>-4.888951992565149</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8682152656119644</v>
+        <v>0.8665286221111927</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4567617659873111</v>
+        <v>-0.4861684266984341</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.548408783858613</v>
+        <v>2.530764787431939</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.709261124020751</v>
+        <v>-4.713477732772679</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9429722015207398</v>
+        <v>0.9412855580199684</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4567617659873111</v>
+        <v>-0.4861684266984341</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.552976015850401</v>
+        <v>2.535332019423727</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.820197376662</v>
+        <v>-4.824413985413928</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8986091743510376</v>
+        <v>0.8969225308502664</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4567617659873111</v>
+        <v>-0.4861684266984341</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.552987489737198</v>
+        <v>2.535343493310525</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.023223954205233</v>
+        <v>-5.027440562957161</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.82052992855365</v>
+        <v>0.8188432850528784</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6597883435305445</v>
+        <v>-0.6891950042416675</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.434302928431164</v>
+        <v>2.41665893200449</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.86529835526994</v>
+        <v>-4.869514964021868</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8938725545598996</v>
+        <v>0.8921859110591281</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6597883435305445</v>
+        <v>-0.6891950042416675</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.444475314863296</v>
+        <v>2.426831318436622</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.013619609081069</v>
+        <v>-5.017836217832997</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8294903236093085</v>
+        <v>0.8278036801085369</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6597883435305445</v>
+        <v>-0.6891950042416675</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.439421585437157</v>
+        <v>2.421777589010483</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.014802693732129</v>
+        <v>-5.019019302484057</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8207928651934098</v>
+        <v>0.8191062216926381</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.665431391997056</v>
+        <v>-0.694838052708179</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.427811531801775</v>
+        <v>2.410167535375102</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.891674986738046</v>
+        <v>-4.895891595489974</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8705958210241445</v>
+        <v>0.868909177523373</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.665431391997056</v>
+        <v>-0.694838052708179</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.428363404834877</v>
+        <v>2.410719408408203</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.798864505287186</v>
+        <v>-4.803081114039115</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8369927054958539</v>
+        <v>0.8353060619950825</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5726209105461967</v>
+        <v>-0.6020275712573196</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.413322385596758</v>
+        <v>2.395678389170084</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.750301453066156</v>
+        <v>-4.754518061818085</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8582914023088668</v>
+        <v>0.8566047588080954</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5240578583251665</v>
+        <v>-0.5534645190362895</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.444333692853977</v>
+        <v>2.426689696427303</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.637630234829906</v>
+        <v>-4.641846843581835</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8984355981150898</v>
+        <v>0.8967489546143184</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4113866400889163</v>
+        <v>-0.4407933008000393</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.50701213230745</v>
+        <v>2.489368135880776</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.525253233647233</v>
+        <v>-4.529469842399162</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9488776944188262</v>
+        <v>0.9471910509180548</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4113866400889163</v>
+        <v>-0.4407933008000393</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.512503428138118</v>
+        <v>2.494859431711443</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.723487802533964</v>
+        <v>-4.727704411285893</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8810810686326729</v>
+        <v>0.8793944251319017</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6096212089756469</v>
+        <v>-0.6390278696867698</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.405059888574618</v>
+        <v>2.387415892147944</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.806489083559243</v>
+        <v>-4.810705692311172</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6862362762232146</v>
+        <v>0.6845496327224434</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6281920935028207</v>
+        <v>-0.6575987542139436</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.232273077858967</v>
+        <v>2.214629081432293</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.647294811502666</v>
+        <v>-4.651511420254595</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.870063645765051</v>
+        <v>0.8683770022642796</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6281920935028207</v>
+        <v>-0.6575987542139436</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.352422738578173</v>
+        <v>2.334778742151499</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,13 +46470,13 @@
         <v>2.537840637876454</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.647294811502666</v>
+        <v>-4.651511420254595</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.870063645765051</v>
+        <v>0.8683770022642796</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6281920935028207</v>
+        <v>-0.6575987542139436</v>
       </c>
       <c r="G1953" t="n">
         <v>2.530904434862822</v>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-27.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.9%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.0%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>135.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-708.7%</t>
+          <t>-693.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.3%</t>
+          <t>444.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-626.7%</t>
+          <t>-594.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-277.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-132.5%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-289.4%</t>
+          <t>-265.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-332.9%</t>
+          <t>-321.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.7%</t>
+          <t>-152.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-289.8%</t>
+          <t>-271.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-200.1%</t>
+          <t>-193.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-192.9%</t>
+          <t>-190.5%</t>
         </is>
       </c>
     </row>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.137727596312753</v>
+        <v>-3.983747216515799</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.484412198368014</v>
+        <v>1.546004350286795</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.601495316318674</v>
+        <v>-0.4826077697737151</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.778962471415658</v>
+        <v>2.850294999342633</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.495377946551101</v>
+        <v>-4.341397566754146</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.337458116928932</v>
+        <v>1.399050268847714</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9591456665570222</v>
+        <v>-0.8402581200120632</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.560478319928907</v>
+        <v>2.631810847855882</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.804612049547152</v>
+        <v>-4.650631669750197</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.215537402430771</v>
+        <v>1.277129554349553</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9591456665570222</v>
+        <v>-0.8402581200120632</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.562251246629166</v>
+        <v>2.633583774556142</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.236417842696939</v>
+        <v>-5.082437462899985</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.029147972638261</v>
+        <v>1.090740124557043</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.095563162998289</v>
+        <v>-0.9766756164533302</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.466733636231811</v>
+        <v>2.538066164158786</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.471111836829492</v>
+        <v>-5.317131457032537</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9235551499873305</v>
+        <v>0.9851473019061125</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.089226895769034</v>
+        <v>-0.9703393492240751</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.458820171571454</v>
+        <v>2.53015269949843</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.806774484059944</v>
+        <v>-5.652794104262989</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7878706827511146</v>
+        <v>0.8494628346698967</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.089226895769034</v>
+        <v>-0.9703393492240751</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.45740076322742</v>
+        <v>2.528733291154395</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.170400728960257</v>
+        <v>-6.016420349163303</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6489077450252307</v>
+        <v>0.7104998969440128</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.18744853263616</v>
+        <v>-1.068560986091201</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.404955341341386</v>
+        <v>2.476287869268361</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.535528111599004</v>
+        <v>-6.381547731802049</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5021113069755638</v>
+        <v>0.5637034588943455</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.483759316935172</v>
+        <v>-1.364871770390213</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.226423385767809</v>
+        <v>2.297755913694785</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.944116888779682</v>
+        <v>-6.790136508982728</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3374373401180515</v>
+        <v>0.3990294920368331</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.773460547570892</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.980031663474161</v>
+        <v>2.051364191401137</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.357099372920776</v>
+        <v>-7.203118993123822</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1674297789330748</v>
+        <v>0.229021930851856</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.773460547570892</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.975217095945622</v>
+        <v>2.046549623872598</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.773491247207773</v>
+        <v>-7.61951086741082</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.001132920172846941</v>
+        <v>0.06045923174593426</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.773460547570892</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.973211146554499</v>
+        <v>2.044543674481475</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.150168257737617</v>
+        <v>-7.996187877940664</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1415450337161053</v>
+        <v>-0.07995288179732452</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.773460547570892</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.983469837223178</v>
+        <v>2.054802365150154</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.496043079722426</v>
+        <v>-8.342062699925473</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2837953973643339</v>
+        <v>-0.2222032454455527</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.773460547570892</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.979569402368874</v>
+        <v>2.050901930295849</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.658185350185519</v>
+        <v>-8.504204970388566</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3502473854945705</v>
+        <v>-0.2886552335757888</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.892348094115851</v>
+        <v>-1.773460547570892</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.977974322423875</v>
+        <v>2.04930685035085</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.954846691995717</v>
+        <v>-8.800866312198764</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4651329462894416</v>
+        <v>-0.4035407943706599</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.961091229849729</v>
+        <v>-1.84220368330477</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.940507416912756</v>
+        <v>2.011839944839731</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.388195800105953</v>
+        <v>-9.234215420308999</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6424988940679386</v>
+        <v>-0.5809067421491569</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.961091229849729</v>
+        <v>-1.84220368330477</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.936481112378353</v>
+        <v>2.007813640305328</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.771197188848584</v>
+        <v>-9.61721680905163</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.795801550886575</v>
+        <v>-0.7342093989677938</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.961091229849729</v>
+        <v>-1.84220368330477</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.936379011056768</v>
+        <v>2.007711538983744</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.928596069061705</v>
+        <v>-9.774615689264751</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8561895870003933</v>
+        <v>-0.7945974350816116</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.11849011006285</v>
+        <v>-1.999602563517892</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.844511198900326</v>
+        <v>1.915843726827301</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.28812639156571</v>
+        <v>-10.13414601176875</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9946514127039441</v>
+        <v>-0.9330592607851624</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.11849011006285</v>
+        <v>-1.999602563517892</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.849861502198376</v>
+        <v>1.921194030125351</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.61452642023072</v>
+        <v>-10.46054604043377</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.117295404212772</v>
+        <v>-1.05570325229399</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.444890138727863</v>
+        <v>-2.326002592182904</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.661937504956546</v>
+        <v>1.733270032883521</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.83367538830492</v>
+        <v>-10.67969500850796</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.201913240820681</v>
+        <v>-1.1403210889019</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.664039106802061</v>
+        <v>-2.545151560257102</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.533489874733796</v>
+        <v>1.604822402660772</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.82998446334851</v>
+        <v>-10.67600408355155</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.200436870838117</v>
+        <v>-1.138844718919336</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.664039106802061</v>
+        <v>-2.545151560257102</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.533489874733796</v>
+        <v>1.604822402660772</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.03424263867837</v>
+        <v>-10.88026225888142</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.27662694385142</v>
+        <v>-1.215034791932639</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.79167805141605</v>
+        <v>-2.672790504871091</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.462419705084045</v>
+        <v>1.533752233011021</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.25228041030955</v>
+        <v>-11.09830003051259</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.359359498019455</v>
+        <v>-1.297767346100674</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.966448819511949</v>
+        <v>-2.84756127296699</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.362039798710942</v>
+        <v>1.433372326637917</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.1788105786421</v>
+        <v>-11.02483019884514</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.314599863859055</v>
+        <v>-1.253007711940273</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.8929789878445</v>
+        <v>-2.774091441299541</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.421493399204832</v>
+        <v>1.492825927131808</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.35393499602864</v>
+        <v>-11.19995461623169</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.370094410066155</v>
+        <v>-1.308502258147374</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.068103405231044</v>
+        <v>-2.949215858686085</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.330973969520423</v>
+        <v>1.402306497447398</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.58838709004313</v>
+        <v>-11.43440671024618</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.471094412573547</v>
+        <v>-1.409502260654766</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.068103405231044</v>
+        <v>-2.949215858686085</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.323754804618827</v>
+        <v>1.395087332545802</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.87619093458037</v>
+        <v>-11.72221055478342</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.592888141162419</v>
+        <v>-1.531295989243637</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.355907249768282</v>
+        <v>-3.237019703223323</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.144400307122508</v>
+        <v>1.215732835049483</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.10601538174419</v>
+        <v>-11.95203500194724</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.683702130189393</v>
+        <v>-1.622109978270611</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.518554786838443</v>
+        <v>-3.399667240293484</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.047927574718968</v>
+        <v>1.119260102645943</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.33804430148046</v>
+        <v>-12.1840639216835</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.773819969454782</v>
+        <v>-1.712227817536002</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.580567484026866</v>
+        <v>-3.461679937481907</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.013413685035028</v>
+        <v>1.084746212962004</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.28602878751164</v>
+        <v>-12.13204840771469</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.749023428180856</v>
+        <v>-1.687431276262075</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.580567484026866</v>
+        <v>-3.461679937481907</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.017404020721429</v>
+        <v>1.088736548648404</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.42770062923576</v>
+        <v>-12.27372024943881</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.807167391769246</v>
+        <v>-1.745575239850464</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.580567484026866</v>
+        <v>-3.461679937481907</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.015928793822687</v>
+        <v>1.087261321749663</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.37810978481093</v>
+        <v>-12.22412940501398</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.77227764383444</v>
+        <v>-1.710685491915659</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.530976639602032</v>
+        <v>-3.412089093057073</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.06073671064246</v>
+        <v>1.132069238569435</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.17895767757383</v>
+        <v>-12.02497729777688</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.705667934586284</v>
+        <v>-1.644075782667502</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.365654113652219</v>
+        <v>-3.24676656710726</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.146879092565665</v>
+        <v>1.218211620492641</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.95311252485442</v>
+        <v>-11.79913214505747</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.60575080046231</v>
+        <v>-1.544158648543529</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.323727438065055</v>
+        <v>-3.204839891520096</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.181614170954172</v>
+        <v>1.252946698881147</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.82853386851683</v>
+        <v>-11.67455348871987</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.554780193371215</v>
+        <v>-1.493188041452434</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.323727438065055</v>
+        <v>-3.204839891520096</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.182753315510231</v>
+        <v>1.254085843437206</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.88142915656111</v>
+        <v>-11.61394165866795</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.573304534426821</v>
+        <v>-1.466309535269558</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.318772091976609</v>
+        <v>-3.139468565941552</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.188360297325406</v>
+        <v>1.29594241294644</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.59752042563236</v>
+        <v>-11.33003292773921</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.454007337816686</v>
+        <v>-1.347012338659422</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.318772091976609</v>
+        <v>-3.139468565941552</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.194094001564043</v>
+        <v>1.301676117185077</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.48209950149427</v>
+        <v>-11.21461200360111</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.417576230555312</v>
+        <v>-1.310581231398048</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.024047641803457</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.253609293653035</v>
+        <v>1.361191409274069</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.2182626342902</v>
+        <v>-10.95077513639704</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.321924964986592</v>
+        <v>-1.214929965829329</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.024047641803457</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.243725812340127</v>
+        <v>1.351307927961161</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9510208334218</v>
+        <v>-10.68353333552864</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.216862805138607</v>
+        <v>-1.109867805981343</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.203351167838513</v>
+        <v>-3.024047641803457</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.241891251840753</v>
+        <v>1.349473367461788</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.82771490494358</v>
+        <v>-10.56022740705042</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.16784074872078</v>
+        <v>-1.060845749563516</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.11393349671095</v>
+        <v>-2.934629970675894</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.29524153954383</v>
+        <v>1.402823655164864</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.80376136396762</v>
+        <v>-10.53627386607447</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.157590826184903</v>
+        <v>-1.050595827027639</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.089979955734993</v>
+        <v>-2.910676429699937</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.310282170274899</v>
+        <v>1.417864285895932</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.53970142564483</v>
+        <v>-10.27221392775167</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.065227167017536</v>
+        <v>-0.958232167860273</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.825920017412197</v>
+        <v>-2.64661649137714</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.455457817106824</v>
+        <v>1.563039932727858</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.83262180213999</v>
+        <v>-9.565134304246831</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7851823512759024</v>
+        <v>-0.6781873521186386</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.825920017412197</v>
+        <v>-2.64661649137714</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.452670783446523</v>
+        <v>1.560252899067557</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.792437503773799</v>
+        <v>-9.52495000588064</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7687650080415849</v>
+        <v>-0.661770008884321</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.785735719046006</v>
+        <v>-2.606432193010949</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.477124986354079</v>
+        <v>1.584707101975113</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.712367708235995</v>
+        <v>-9.444880210342836</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.737370268605706</v>
+        <v>-0.6303752694484426</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.705665923508202</v>
+        <v>-2.526362397473145</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.524533684897519</v>
+        <v>1.632115800518552</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.478886486006395</v>
+        <v>-9.211398988113238</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.636053350876014</v>
+        <v>-0.529058351718751</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.472184701278603</v>
+        <v>-2.292881175243547</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.67254684707313</v>
+        <v>1.780128962694164</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.299177955862522</v>
+        <v>-9.031690457969365</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5670621491314236</v>
+        <v>-0.4600671499741606</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.415013197115907</v>
+        <v>-2.235709671080851</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.703957539257788</v>
+        <v>1.811539654878822</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.166902482231635</v>
+        <v>-8.899414984338478</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5187844729320417</v>
+        <v>-0.4117894737747787</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.282737723485021</v>
+        <v>-2.103434197449964</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.778690310183347</v>
+        <v>1.886272425804381</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.976302807558481</v>
+        <v>-8.708815309665324</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4397295423751437</v>
+        <v>-0.3327345432178808</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.092138048811868</v>
+        <v>-1.912834522776812</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.895865175674876</v>
+        <v>2.00344729129591</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.7273030088749</v>
+        <v>-8.459815510981743</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3272232816780525</v>
+        <v>-0.2202282825207895</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.092138048811868</v>
+        <v>-1.912834522776812</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.908771516898534</v>
+        <v>2.016353632519568</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.832892998648004</v>
+        <v>-8.565405500754848</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4974352071865127</v>
+        <v>-0.3904402080292502</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.197728038584973</v>
+        <v>-2.018424512549916</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.717441593435453</v>
+        <v>1.825023709056487</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.851627900766601</v>
+        <v>-8.584140402873444</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4563848261568655</v>
+        <v>-0.3493898269996025</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.197728038584973</v>
+        <v>-2.018424512549916</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.765985935312539</v>
+        <v>1.873568050933573</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.703687859359002</v>
+        <v>-8.436200361465845</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5170877322819933</v>
+        <v>-0.4100927331247304</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.177407122676415</v>
+        <v>-1.998103596641358</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.658299562169506</v>
+        <v>1.76588167779054</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.67945922297003</v>
+        <v>-8.411971725076873</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5161102639798822</v>
+        <v>-0.4091152648226197</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.153178486287443</v>
+        <v>-1.973874960252386</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.664122757749412</v>
+        <v>1.771704873370446</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.635910816199338</v>
+        <v>-8.368423318306181</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5056515133666988</v>
+        <v>-0.3986565142094363</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.153178486287443</v>
+        <v>-1.973874960252386</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.657162145654318</v>
+        <v>1.764744261275353</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.39376242274548</v>
+        <v>-8.126274924852323</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3943298016040124</v>
+        <v>-0.2873348024467499</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.153178486287443</v>
+        <v>-1.973874960252386</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.671624500035461</v>
+        <v>1.779206615656496</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.330533050977133</v>
+        <v>-8.063045553083976</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3745059324374784</v>
+        <v>-0.2675109332802159</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.153178486287443</v>
+        <v>-1.973874960252386</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.666156620494657</v>
+        <v>1.773738736115691</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.207241916160003</v>
+        <v>-7.939754418266845</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3276913845000498</v>
+        <v>-0.2206963853427868</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.029887351470312</v>
+        <v>-1.850583825435256</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.737629395395512</v>
+        <v>1.845211511016546</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.18609271725656</v>
+        <v>-7.918605219363402</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3115307267013474</v>
+        <v>-0.204535727544084</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.008738152566869</v>
+        <v>-1.829434626531812</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.758019892974903</v>
+        <v>1.865602008595937</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.942327275273116</v>
+        <v>-7.674839777379957</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2182438415609194</v>
+        <v>-0.1112488424036555</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.008738152566869</v>
+        <v>-1.829434626531812</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.753800601321953</v>
+        <v>1.861382716942988</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.678299208079856</v>
+        <v>-7.410811710186698</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1105083007635992</v>
+        <v>-0.003513301606335784</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.627569227715859</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.877044154531541</v>
+        <v>1.984626270152575</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.428448814130782</v>
+        <v>-7.160961316237623</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.01782606820026755</v>
+        <v>0.0891689309569963</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.627569227715859</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.869786229515244</v>
+        <v>1.977368345136278</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.25255672166335</v>
+        <v>-6.985069223770191</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.0561298923073541</v>
+        <v>0.1631248914646175</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.806872753750915</v>
+        <v>-1.627569227715859</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.873385353035892</v>
+        <v>1.980967468656926</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.081110258640886</v>
+        <v>-6.813622760747728</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1380359835708931</v>
+        <v>0.2450309827281569</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.635426290728452</v>
+        <v>-1.456122764693395</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.989580736903924</v>
+        <v>2.097162852524958</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.856077258972063</v>
+        <v>-6.588589761078905</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2270696610547196</v>
+        <v>0.334064660211983</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.410393291059629</v>
+        <v>-1.231089765024572</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.123621014321515</v>
+        <v>2.231203129942549</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.641442881335657</v>
+        <v>-6.373955383442498</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3176182131635996</v>
+        <v>0.424613212320863</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.195758913423222</v>
+        <v>-1.016455387388166</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.257096441957676</v>
+        <v>2.36467855757871</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.374842524361305</v>
+        <v>-6.107355026468146</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4054526147371358</v>
+        <v>0.5124476138943992</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.195758913423222</v>
+        <v>-1.016455387388166</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.238290700741472</v>
+        <v>2.345872816362506</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.134412027556444</v>
+        <v>-5.866924529663286</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5033678900839571</v>
+        <v>0.610362889241221</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9553284166183622</v>
+        <v>-0.7760248905833054</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.384292075449265</v>
+        <v>2.491874191070299</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.891621219906999</v>
+        <v>-5.62413372201384</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6044135269785555</v>
+        <v>0.7114085261358194</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9553284166183622</v>
+        <v>-0.7760248905833054</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.388221389284086</v>
+        <v>2.49580350490512</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.775681370281814</v>
+        <v>-5.508193872388655</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.65146805074597</v>
+        <v>0.7584630499032334</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8785066856022383</v>
+        <v>-0.6992031595671815</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.4349930118111</v>
+        <v>2.542575127432134</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.533025781858651</v>
+        <v>-5.265538283965492</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7455283573352283</v>
+        <v>0.8525233564924921</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8785066856022383</v>
+        <v>-0.6992031595671815</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.431991083031094</v>
+        <v>2.539573198652127</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.31300498382164</v>
+        <v>-5.045517485928482</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8351157135606466</v>
+        <v>0.9421107127179105</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7372868405342581</v>
+        <v>-0.5579833144992012</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.518302027082496</v>
+        <v>2.62588414270353</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.113756353916831</v>
+        <v>-4.846268856023673</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9307093483243936</v>
+        <v>1.037704347481657</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7372868405342581</v>
+        <v>-0.5579833144992012</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.534196209884319</v>
+        <v>2.641778325505353</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.954241250397462</v>
+        <v>-4.686753752504303</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9956612341724436</v>
+        <v>1.102656233329707</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5777717370148882</v>
+        <v>-0.3984682109798313</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.631051116436243</v>
+        <v>2.738633232057277</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.809569105297724</v>
+        <v>-4.542081607404565</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.063618194773778</v>
+        <v>1.170613193931042</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4330995919151507</v>
+        <v>-0.2537960658800939</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.727942506057525</v>
+        <v>2.835524621678559</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.869443932655416</v>
+        <v>-4.601956434762258</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.025705755232127</v>
+        <v>1.132700754389391</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4929744192728429</v>
+        <v>-0.313670893237786</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.678055101044336</v>
+        <v>2.78563721666537</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.782644434876408</v>
+        <v>-4.515156936983249</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.082826047666297</v>
+        <v>1.18982104682356</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4929744192728429</v>
+        <v>-0.313670893237786</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.700455594366902</v>
+        <v>2.808037709987936</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.785114141338214</v>
+        <v>-4.517626643445055</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.081910566454986</v>
+        <v>1.18890556561225</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.495444125734649</v>
+        <v>-0.3161405996995922</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.69904617186323</v>
+        <v>2.806628287484264</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.853484327662224</v>
+        <v>-4.585996829769066</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.065569414400084</v>
+        <v>1.172564413557348</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.3068649006633772</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.715618513759661</v>
+        <v>2.823200629380695</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.857958833236443</v>
+        <v>-4.590471335343285</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.054216320802288</v>
+        <v>1.161211319959552</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.3068649006633772</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.706055222391552</v>
+        <v>2.813637338012587</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.888951992565149</v>
+        <v>-4.62146449467199</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8665286221111927</v>
+        <v>0.9735236212684562</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.3068649006633772</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.530764787431939</v>
+        <v>2.638346903052974</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.713477732772679</v>
+        <v>-4.44599023487952</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9412855580199684</v>
+        <v>1.048280557177232</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.3068649006633772</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.535332019423727</v>
+        <v>2.642914135044761</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.824413985413928</v>
+        <v>-4.556926487520769</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8969225308502664</v>
+        <v>1.00391753000753</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4861684266984341</v>
+        <v>-0.3068649006633772</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.535343493310525</v>
+        <v>2.642925608931559</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.027440562957161</v>
+        <v>-4.759953065064003</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8188432850528784</v>
+        <v>0.925838284210142</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6891950042416675</v>
+        <v>-0.5098914782066106</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.41665893200449</v>
+        <v>2.524241047625524</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.869514964021868</v>
+        <v>-4.602027466128709</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8921859110591281</v>
+        <v>0.9991809102163915</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6891950042416675</v>
+        <v>-0.5098914782066106</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.426831318436622</v>
+        <v>2.534413434057657</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.017836217832997</v>
+        <v>-4.750348719939838</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8278036801085369</v>
+        <v>0.9347986792658005</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6891950042416675</v>
+        <v>-0.5098914782066106</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.421777589010483</v>
+        <v>2.529359704631517</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.019019302484057</v>
+        <v>-4.751531804590899</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8191062216926381</v>
+        <v>0.9261012208499018</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.694838052708179</v>
+        <v>-0.5155345266731222</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.410167535375102</v>
+        <v>2.517749650996135</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.895891595489974</v>
+        <v>-4.628404097596816</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.868909177523373</v>
+        <v>0.9759041766806367</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.694838052708179</v>
+        <v>-0.5155345266731222</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.410719408408203</v>
+        <v>2.518301524029237</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.803081114039115</v>
+        <v>-4.535593616145956</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8353060619950825</v>
+        <v>0.9423010611523461</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6020275712573196</v>
+        <v>-0.4227240452222628</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.395678389170084</v>
+        <v>2.503260504791118</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.754518061818085</v>
+        <v>-4.487030563924926</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8566047588080954</v>
+        <v>0.9635997579653588</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5534645190362895</v>
+        <v>-0.3741609930012326</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.426689696427303</v>
+        <v>2.534271812048337</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.641846843581835</v>
+        <v>-4.374359345688676</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8967489546143184</v>
+        <v>1.003743953771582</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4407933008000393</v>
+        <v>-0.2614897747649824</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.489368135880776</v>
+        <v>2.596950251501811</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.529469842399162</v>
+        <v>-4.261982344506003</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9471910509180548</v>
+        <v>1.054186050075318</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4407933008000393</v>
+        <v>-0.2614897747649824</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.494859431711443</v>
+        <v>2.602441547332478</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.727704411285893</v>
+        <v>-4.460216913392734</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8793944251319017</v>
+        <v>0.9863894242891651</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6390278696867698</v>
+        <v>-0.459724343651713</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.387415892147944</v>
+        <v>2.494998007768978</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.810705692311172</v>
+        <v>-4.543218194418013</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6845496327224434</v>
+        <v>0.7915446318797068</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6575987542139436</v>
+        <v>-0.4782952281788868</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.214629081432293</v>
+        <v>2.322211197053327</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.651511420254595</v>
+        <v>-4.205717657059198</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8683770022642796</v>
+        <v>1.046694507542438</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6575987542139436</v>
+        <v>-0.4782952281788868</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.334778742151499</v>
+        <v>2.442360857772533</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.383035908391638</v>
+        <v>3.848979649464605</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.537840637876454</v>
+        <v>2.841977702139982</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.651511420254595</v>
+        <v>-4.332564333405325</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8683770022642796</v>
+        <v>1.108595544464104</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6575987542139436</v>
+        <v>-0.4782952281788868</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.530904434862822</v>
+        <v>2.55500056523265</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240503.xlsx
+++ b/tame_output/ON/bt/strategyON_20240503.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-37.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>136.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-693.3%</t>
+          <t>-708.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.9%</t>
+          <t>440.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.8%</t>
+          <t>-609.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.7%</t>
+          <t>-283.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-45.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-125.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-265.4%</t>
+          <t>-280.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-321.0%</t>
+          <t>-332.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-164.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.8%</t>
+          <t>-301.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-193.0%</t>
+          <t>-200.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-190.5%</t>
+          <t>-218.2%</t>
         </is>
       </c>
     </row>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.983747216515799</v>
+        <v>-4.137727596312753</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.546004350286795</v>
+        <v>1.484412198368014</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4826077697737151</v>
+        <v>-0.601495316318674</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.850294999342633</v>
+        <v>2.778962471415658</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.341397566754146</v>
+        <v>-4.495377946551101</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.399050268847714</v>
+        <v>1.337458116928932</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8402581200120632</v>
+        <v>-0.9591456665570222</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.631810847855882</v>
+        <v>2.560478319928907</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.650631669750197</v>
+        <v>-4.804612049547152</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.277129554349553</v>
+        <v>1.215537402430771</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8402581200120632</v>
+        <v>-0.9591456665570222</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.633583774556142</v>
+        <v>2.562251246629166</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.082437462899985</v>
+        <v>-5.236417842696939</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.090740124557043</v>
+        <v>1.029147972638261</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9766756164533302</v>
+        <v>-1.095563162998289</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.538066164158786</v>
+        <v>2.466733636231811</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.317131457032537</v>
+        <v>-5.471111836829492</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9851473019061125</v>
+        <v>0.9235551499873305</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9703393492240751</v>
+        <v>-1.089226895769034</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.53015269949843</v>
+        <v>2.458820171571454</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.652794104262989</v>
+        <v>-5.806774484059944</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8494628346698967</v>
+        <v>0.7878706827511146</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9703393492240751</v>
+        <v>-1.089226895769034</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.528733291154395</v>
+        <v>2.45740076322742</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.016420349163303</v>
+        <v>-6.170400728960257</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7104998969440128</v>
+        <v>0.6489077450252307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.068560986091201</v>
+        <v>-1.18744853263616</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.476287869268361</v>
+        <v>2.404955341341386</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.381547731802049</v>
+        <v>-6.535528111599004</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5637034588943455</v>
+        <v>0.5021113069755638</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.364871770390213</v>
+        <v>-1.483759316935172</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.297755913694785</v>
+        <v>2.226423385767809</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.790136508982728</v>
+        <v>-6.944116888779682</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3990294920368331</v>
+        <v>0.3374373401180515</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.773460547570892</v>
+        <v>-1.892348094115851</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.051364191401137</v>
+        <v>1.980031663474161</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.203118993123822</v>
+        <v>-7.357099372920776</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.229021930851856</v>
+        <v>0.1674297789330748</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.773460547570892</v>
+        <v>-1.892348094115851</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.046549623872598</v>
+        <v>1.975217095945622</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.61951086741082</v>
+        <v>-7.773491247207773</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.06045923174593426</v>
+        <v>-0.001132920172846941</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.773460547570892</v>
+        <v>-1.892348094115851</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.044543674481475</v>
+        <v>1.973211146554499</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.996187877940664</v>
+        <v>-8.150168257737617</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.07995288179732452</v>
+        <v>-0.1415450337161053</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.773460547570892</v>
+        <v>-1.892348094115851</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.054802365150154</v>
+        <v>1.983469837223178</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.342062699925473</v>
+        <v>-8.496043079722426</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2222032454455527</v>
+        <v>-0.2837953973643339</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.773460547570892</v>
+        <v>-1.892348094115851</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.050901930295849</v>
+        <v>1.979569402368874</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.504204970388566</v>
+        <v>-8.658185350185519</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2886552335757888</v>
+        <v>-0.3502473854945705</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.773460547570892</v>
+        <v>-1.892348094115851</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.04930685035085</v>
+        <v>1.977974322423875</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.800866312198764</v>
+        <v>-8.954846691995717</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4035407943706599</v>
+        <v>-0.4651329462894416</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.84220368330477</v>
+        <v>-1.961091229849729</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.011839944839731</v>
+        <v>1.940507416912756</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.234215420308999</v>
+        <v>-9.388195800105953</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5809067421491569</v>
+        <v>-0.6424988940679386</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.84220368330477</v>
+        <v>-1.961091229849729</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.007813640305328</v>
+        <v>1.936481112378353</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.61721680905163</v>
+        <v>-9.771197188848584</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7342093989677938</v>
+        <v>-0.795801550886575</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.84220368330477</v>
+        <v>-1.961091229849729</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.007711538983744</v>
+        <v>1.936379011056768</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.774615689264751</v>
+        <v>-9.928596069061705</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7945974350816116</v>
+        <v>-0.8561895870003933</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.999602563517892</v>
+        <v>-2.11849011006285</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.915843726827301</v>
+        <v>1.844511198900326</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13414601176875</v>
+        <v>-10.28812639156571</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9330592607851624</v>
+        <v>-0.9946514127039441</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.999602563517892</v>
+        <v>-2.11849011006285</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.921194030125351</v>
+        <v>1.849861502198376</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46054604043377</v>
+        <v>-10.61452642023072</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05570325229399</v>
+        <v>-1.117295404212772</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.326002592182904</v>
+        <v>-2.444890138727863</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.733270032883521</v>
+        <v>1.661937504956546</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.67969500850796</v>
+        <v>-10.83367538830492</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.1403210889019</v>
+        <v>-1.201913240820681</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.545151560257102</v>
+        <v>-2.664039106802061</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.604822402660772</v>
+        <v>1.533489874733796</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67600408355155</v>
+        <v>-10.82998446334851</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.138844718919336</v>
+        <v>-1.200436870838117</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.545151560257102</v>
+        <v>-2.664039106802061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.604822402660772</v>
+        <v>1.533489874733796</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88026225888142</v>
+        <v>-11.03424263867837</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.215034791932639</v>
+        <v>-1.27662694385142</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.672790504871091</v>
+        <v>-2.79167805141605</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.533752233011021</v>
+        <v>1.462419705084045</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.09830003051259</v>
+        <v>-11.25228041030955</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.297767346100674</v>
+        <v>-1.359359498019455</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.84756127296699</v>
+        <v>-2.966448819511949</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.433372326637917</v>
+        <v>1.362039798710942</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02483019884514</v>
+        <v>-11.1788105786421</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.253007711940273</v>
+        <v>-1.314599863859055</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.774091441299541</v>
+        <v>-2.8929789878445</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.492825927131808</v>
+        <v>1.421493399204832</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.19995461623169</v>
+        <v>-11.35393499602864</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.308502258147374</v>
+        <v>-1.370094410066155</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.949215858686085</v>
+        <v>-3.068103405231044</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.402306497447398</v>
+        <v>1.330973969520423</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.43440671024618</v>
+        <v>-11.58838709004313</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.409502260654766</v>
+        <v>-1.471094412573547</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.949215858686085</v>
+        <v>-3.068103405231044</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.395087332545802</v>
+        <v>1.323754804618827</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72221055478342</v>
+        <v>-11.87619093458037</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.531295989243637</v>
+        <v>-1.592888141162419</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.237019703223323</v>
+        <v>-3.355907249768282</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.215732835049483</v>
+        <v>1.144400307122508</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95203500194724</v>
+        <v>-12.10601538174419</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.622109978270611</v>
+        <v>-1.683702130189393</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.399667240293484</v>
+        <v>-3.518554786838443</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.119260102645943</v>
+        <v>1.047927574718968</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.1840639216835</v>
+        <v>-12.33804430148046</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.712227817536002</v>
+        <v>-1.773819969454782</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.461679937481907</v>
+        <v>-3.580567484026866</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.084746212962004</v>
+        <v>1.013413685035028</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13204840771469</v>
+        <v>-12.28602878751164</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.687431276262075</v>
+        <v>-1.749023428180856</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.461679937481907</v>
+        <v>-3.580567484026866</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.088736548648404</v>
+        <v>1.017404020721429</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27372024943881</v>
+        <v>-12.42770062923576</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.745575239850464</v>
+        <v>-1.807167391769246</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.461679937481907</v>
+        <v>-3.580567484026866</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.087261321749663</v>
+        <v>1.015928793822687</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.22412940501398</v>
+        <v>-12.37810978481093</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.710685491915659</v>
+        <v>-1.77227764383444</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.412089093057073</v>
+        <v>-3.530976639602032</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.132069238569435</v>
+        <v>1.06073671064246</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.02497729777688</v>
+        <v>-12.17895767757383</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.644075782667502</v>
+        <v>-1.705667934586284</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.24676656710726</v>
+        <v>-3.365654113652219</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.218211620492641</v>
+        <v>1.146879092565665</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.79913214505747</v>
+        <v>-11.95311252485442</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.544158648543529</v>
+        <v>-1.60575080046231</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.204839891520096</v>
+        <v>-3.323727438065055</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.252946698881147</v>
+        <v>1.181614170954172</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.67455348871987</v>
+        <v>-11.82853386851683</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.493188041452434</v>
+        <v>-1.554780193371215</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.204839891520096</v>
+        <v>-3.323727438065055</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.254085843437206</v>
+        <v>1.182753315510231</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.61394165866795</v>
+        <v>-11.88142915656111</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.466309535269558</v>
+        <v>-1.573304534426821</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.139468565941552</v>
+        <v>-3.318772091976609</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.29594241294644</v>
+        <v>1.188360297325406</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.33003292773921</v>
+        <v>-11.59752042563236</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.347012338659422</v>
+        <v>-1.454007337816686</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.139468565941552</v>
+        <v>-3.318772091976609</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.301676117185077</v>
+        <v>1.194094001564043</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.21461200360111</v>
+        <v>-11.48209950149427</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.310581231398048</v>
+        <v>-1.417576230555312</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.024047641803457</v>
+        <v>-3.203351167838513</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.361191409274069</v>
+        <v>1.253609293653035</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.95077513639704</v>
+        <v>-11.2182626342902</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.214929965829329</v>
+        <v>-1.321924964986592</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.024047641803457</v>
+        <v>-3.203351167838513</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.351307927961161</v>
+        <v>1.243725812340127</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.68353333552864</v>
+        <v>-10.9510208334218</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.109867805981343</v>
+        <v>-1.216862805138607</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.024047641803457</v>
+        <v>-3.203351167838513</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.349473367461788</v>
+        <v>1.241891251840753</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.56022740705042</v>
+        <v>-10.82771490494358</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.060845749563516</v>
+        <v>-1.16784074872078</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.934629970675894</v>
+        <v>-3.11393349671095</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.402823655164864</v>
+        <v>1.29524153954383</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.53627386607447</v>
+        <v>-10.80376136396762</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.050595827027639</v>
+        <v>-1.157590826184903</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.910676429699937</v>
+        <v>-3.089979955734993</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.417864285895932</v>
+        <v>1.310282170274899</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.27221392775167</v>
+        <v>-10.53970142564483</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.958232167860273</v>
+        <v>-1.065227167017536</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.64661649137714</v>
+        <v>-2.825920017412197</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.563039932727858</v>
+        <v>1.455457817106824</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.565134304246831</v>
+        <v>-9.83262180213999</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6781873521186386</v>
+        <v>-0.7851823512759024</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.64661649137714</v>
+        <v>-2.825920017412197</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.560252899067557</v>
+        <v>1.452670783446523</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.52495000588064</v>
+        <v>-9.792437503773799</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.661770008884321</v>
+        <v>-0.7687650080415849</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.606432193010949</v>
+        <v>-2.785735719046006</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.584707101975113</v>
+        <v>1.477124986354079</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.444880210342836</v>
+        <v>-9.712367708235995</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6303752694484426</v>
+        <v>-0.737370268605706</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.526362397473145</v>
+        <v>-2.705665923508202</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.632115800518552</v>
+        <v>1.524533684897519</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.211398988113238</v>
+        <v>-9.478886486006395</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.529058351718751</v>
+        <v>-0.636053350876014</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.292881175243547</v>
+        <v>-2.472184701278603</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.780128962694164</v>
+        <v>1.67254684707313</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.031690457969365</v>
+        <v>-9.299177955862522</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4600671499741606</v>
+        <v>-0.5670621491314236</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.235709671080851</v>
+        <v>-2.415013197115907</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.811539654878822</v>
+        <v>1.703957539257788</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.899414984338478</v>
+        <v>-9.166902482231635</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4117894737747787</v>
+        <v>-0.5187844729320417</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.103434197449964</v>
+        <v>-2.282737723485021</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.886272425804381</v>
+        <v>1.778690310183347</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.708815309665324</v>
+        <v>-8.976302807558481</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3327345432178808</v>
+        <v>-0.4397295423751437</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.912834522776812</v>
+        <v>-2.092138048811868</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.00344729129591</v>
+        <v>1.895865175674876</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.459815510981743</v>
+        <v>-8.7273030088749</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2202282825207895</v>
+        <v>-0.3272232816780525</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.912834522776812</v>
+        <v>-2.092138048811868</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.016353632519568</v>
+        <v>1.908771516898534</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.565405500754848</v>
+        <v>-8.832892998648004</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3904402080292502</v>
+        <v>-0.4974352071865127</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.018424512549916</v>
+        <v>-2.197728038584973</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.825023709056487</v>
+        <v>1.717441593435453</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.584140402873444</v>
+        <v>-8.851627900766601</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3493898269996025</v>
+        <v>-0.4563848261568655</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.018424512549916</v>
+        <v>-2.197728038584973</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.873568050933573</v>
+        <v>1.765985935312539</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.436200361465845</v>
+        <v>-8.703687859359002</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4100927331247304</v>
+        <v>-0.5170877322819933</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.998103596641358</v>
+        <v>-2.177407122676415</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.76588167779054</v>
+        <v>1.658299562169506</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.411971725076873</v>
+        <v>-8.67945922297003</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4091152648226197</v>
+        <v>-0.5161102639798822</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.973874960252386</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.771704873370446</v>
+        <v>1.664122757749412</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.368423318306181</v>
+        <v>-8.635910816199338</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3986565142094363</v>
+        <v>-0.5056515133666988</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.973874960252386</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.764744261275353</v>
+        <v>1.657162145654318</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.126274924852323</v>
+        <v>-8.39376242274548</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2873348024467499</v>
+        <v>-0.3943298016040124</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.973874960252386</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.779206615656496</v>
+        <v>1.671624500035461</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.063045553083976</v>
+        <v>-8.330533050977133</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2675109332802159</v>
+        <v>-0.3745059324374784</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.973874960252386</v>
+        <v>-2.153178486287443</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.773738736115691</v>
+        <v>1.666156620494657</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.939754418266845</v>
+        <v>-8.207241916160003</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2206963853427868</v>
+        <v>-0.3276913845000498</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.850583825435256</v>
+        <v>-2.029887351470312</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.845211511016546</v>
+        <v>1.737629395395512</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.918605219363402</v>
+        <v>-8.18609271725656</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.204535727544084</v>
+        <v>-0.3115307267013474</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.829434626531812</v>
+        <v>-2.008738152566869</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.865602008595937</v>
+        <v>1.758019892974903</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.674839777379957</v>
+        <v>-7.942327275273116</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1112488424036555</v>
+        <v>-0.2182438415609194</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.829434626531812</v>
+        <v>-2.008738152566869</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.861382716942988</v>
+        <v>1.753800601321953</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.410811710186698</v>
+        <v>-7.678299208079856</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.003513301606335784</v>
+        <v>-0.1105083007635992</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.627569227715859</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.984626270152575</v>
+        <v>1.877044154531541</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.160961316237623</v>
+        <v>-7.428448814130782</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0891689309569963</v>
+        <v>-0.01782606820026755</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.627569227715859</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.977368345136278</v>
+        <v>1.869786229515244</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.985069223770191</v>
+        <v>-7.25255672166335</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1631248914646175</v>
+        <v>0.0561298923073541</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.627569227715859</v>
+        <v>-1.806872753750915</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.980967468656926</v>
+        <v>1.873385353035892</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.813622760747728</v>
+        <v>-7.081110258640886</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2450309827281569</v>
+        <v>0.1380359835708931</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.456122764693395</v>
+        <v>-1.635426290728452</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.097162852524958</v>
+        <v>1.989580736903924</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.588589761078905</v>
+        <v>-6.973985296052937</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.334064660211983</v>
+        <v>0.1799064462223701</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.231089765024572</v>
+        <v>-1.528301328140503</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.231203129942549</v>
+        <v>2.052876192072991</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.373955383442498</v>
+        <v>-6.75935091841653</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.424613212320863</v>
+        <v>0.2704549983312501</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.016455387388166</v>
+        <v>-1.313666950504096</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.36467855757871</v>
+        <v>2.186351619709152</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.107355026468146</v>
+        <v>-6.492750561442178</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5124476138943992</v>
+        <v>0.3582893999047863</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.016455387388166</v>
+        <v>-1.313666950504096</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.345872816362506</v>
+        <v>2.167545878492948</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.866924529663286</v>
+        <v>-6.252320064637318</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.610362889241221</v>
+        <v>0.456204675251608</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7760248905833054</v>
+        <v>-1.073236453699236</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.491874191070299</v>
+        <v>2.313547253200742</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.62413372201384</v>
+        <v>-6.009529256987872</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7114085261358194</v>
+        <v>0.5572503121462065</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7760248905833054</v>
+        <v>-1.073236453699236</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.49580350490512</v>
+        <v>2.317476567035562</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.508193872388655</v>
+        <v>-5.893589407362687</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7584630499032334</v>
+        <v>0.6043048359136205</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6992031595671815</v>
+        <v>-0.9964147226831117</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.542575127432134</v>
+        <v>2.364248189562576</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.265538283965492</v>
+        <v>-5.650933818939524</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8525233564924921</v>
+        <v>0.6983651425028792</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6992031595671815</v>
+        <v>-0.9964147226831117</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.539573198652127</v>
+        <v>2.361246260782569</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.045517485928482</v>
+        <v>-5.430913020902514</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9421107127179105</v>
+        <v>0.7879524987282975</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5579833144992012</v>
+        <v>-0.8551948776151315</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.62588414270353</v>
+        <v>2.447557204833972</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.846268856023673</v>
+        <v>-5.231664390997705</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.037704347481657</v>
+        <v>0.8835461334920445</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5579833144992012</v>
+        <v>-0.8551948776151315</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.641778325505353</v>
+        <v>2.463451387635795</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.686753752504303</v>
+        <v>-5.072149287478335</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.102656233329707</v>
+        <v>0.9484980193400943</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3984682109798313</v>
+        <v>-0.6956797740957615</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.738633232057277</v>
+        <v>2.560306294187719</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.542081607404565</v>
+        <v>-4.927477142378597</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.170613193931042</v>
+        <v>1.016454979941429</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2537960658800939</v>
+        <v>-0.5510076289960242</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.835524621678559</v>
+        <v>2.657197683809001</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.601956434762258</v>
+        <v>-4.98735196973629</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.132700754389391</v>
+        <v>0.9785425403997778</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.313670893237786</v>
+        <v>-0.6108824563537163</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.78563721666537</v>
+        <v>2.607310278795812</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.515156936983249</v>
+        <v>-4.900552471957281</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.18982104682356</v>
+        <v>1.035662832833947</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.313670893237786</v>
+        <v>-0.6108824563537163</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.808037709987936</v>
+        <v>2.629710772118378</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.517626643445055</v>
+        <v>-4.903022178419087</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.18890556561225</v>
+        <v>1.034747351622637</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3161405996995922</v>
+        <v>-0.6133521628155225</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.806628287484264</v>
+        <v>2.628301349614706</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.585996829769066</v>
+        <v>-4.971392364743098</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.172564413557348</v>
+        <v>1.018406199567735</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3068649006633772</v>
+        <v>-0.6040764637793076</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.823200629380695</v>
+        <v>2.644873691511137</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.590471335343285</v>
+        <v>-4.849975935116621</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.161211319959552</v>
+        <v>1.057409480050217</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3068649006633772</v>
+        <v>-0.6040764637793076</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.813637338012587</v>
+        <v>2.635310400143029</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.62146449467199</v>
+        <v>-4.880969094445327</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9735236212684562</v>
+        <v>0.8697217813591216</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3068649006633772</v>
+        <v>-0.6040764637793076</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.638346903052974</v>
+        <v>2.460019965183415</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.44599023487952</v>
+        <v>-4.705494834652857</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.048280557177232</v>
+        <v>0.9444787172678972</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3068649006633772</v>
+        <v>-0.6040764637793076</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.642914135044761</v>
+        <v>2.464587197175203</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.556926487520769</v>
+        <v>-4.816431087294106</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.00391753000753</v>
+        <v>0.9001156900981953</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3068649006633772</v>
+        <v>-0.6040764637793076</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.642925608931559</v>
+        <v>2.464598671062001</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.759953065064003</v>
+        <v>-5.019457664837339</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.925838284210142</v>
+        <v>0.8220364443008075</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5098914782066106</v>
+        <v>-0.807103041322541</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.524241047625524</v>
+        <v>2.345914109755966</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.602027466128709</v>
+        <v>-4.861532065902046</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9991809102163915</v>
+        <v>0.895379070307057</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5098914782066106</v>
+        <v>-0.807103041322541</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.534413434057657</v>
+        <v>2.356086496188099</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.750348719939838</v>
+        <v>-5.009853319713175</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9347986792658005</v>
+        <v>0.830996839356466</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5098914782066106</v>
+        <v>-0.807103041322541</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.529359704631517</v>
+        <v>2.351032766761959</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.751531804590899</v>
+        <v>-5.011036404364235</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9261012208499018</v>
+        <v>0.8222993809405672</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5155345266731222</v>
+        <v>-0.8127460897890525</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.517749650996135</v>
+        <v>2.339422713126577</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.628404097596816</v>
+        <v>-4.887908697370152</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9759041766806367</v>
+        <v>0.8721023367713019</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5155345266731222</v>
+        <v>-0.8127460897890525</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.518301524029237</v>
+        <v>2.339974586159679</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.535593616145956</v>
+        <v>-4.795098215919293</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9423010611523461</v>
+        <v>0.8384992212430116</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4227240452222628</v>
+        <v>-0.7199356083381931</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.503260504791118</v>
+        <v>2.32493356692156</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.487030563924926</v>
+        <v>-4.746535163698263</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9635997579653588</v>
+        <v>0.8597979180560242</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3741609930012326</v>
+        <v>-0.671372556117163</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.534271812048337</v>
+        <v>2.355944874178779</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.374359345688676</v>
+        <v>-4.633863945462013</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.003743953771582</v>
+        <v>0.8999421138622474</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2614897747649824</v>
+        <v>-0.5587013378809127</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.596950251501811</v>
+        <v>2.418623313632252</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.261982344506003</v>
+        <v>-4.52148694427934</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.054186050075318</v>
+        <v>0.9503842101659838</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2614897747649824</v>
+        <v>-0.5587013378809127</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.602441547332478</v>
+        <v>2.42411460946292</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.460216913392734</v>
+        <v>-4.71972151316607</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9863894242891651</v>
+        <v>0.8825875843798305</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.459724343651713</v>
+        <v>-0.7569359067676433</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.494998007768978</v>
+        <v>2.31667106989942</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.543218194418013</v>
+        <v>-4.802722794191349</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7915446318797068</v>
+        <v>0.6877427919703722</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4782952281788868</v>
+        <v>-0.775506791294817</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.322211197053327</v>
+        <v>2.143884259183769</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199273</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.205717657059198</v>
+        <v>-4.643528522134773</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.046694507542438</v>
+        <v>0.8715701615122085</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4782952281788868</v>
+        <v>-0.775506791294817</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.442360857772533</v>
+        <v>2.264033919902975</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.848979649464605</v>
+        <v>3.38801110108156</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.841977702139982</v>
+        <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.332564333405325</v>
+        <v>-4.476932778710655</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.108595544464104</v>
+        <v>0.9527214849841785</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4782952281788868</v>
+        <v>-0.775506791294817</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.55500056523265</v>
+        <v>2.278546946005298</v>
       </c>
     </row>
   </sheetData>
